--- a/outputs/01a034a3-641b-70f2-bc46-4a4f5cf27673/Rebekahs-Phase-Two-Ecommerce-Workbook.xlsx
+++ b/outputs/01a034a3-641b-70f2-bc46-4a4f5cf27673/Rebekahs-Phase-Two-Ecommerce-Workbook.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Set" sheetId="1" r:id="R45119153072f49f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Templates &amp; Global" sheetId="2" r:id="R98be9f4e9e28456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product &amp; Content" sheetId="3" r:id="R2c9d7df3488d4e3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions &amp; Access" sheetId="4" r:id="R663f7d8be3804dfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Plan" sheetId="5" r:id="R49a91cb6949d47e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA &amp; Launch Gates" sheetId="6" r:id="Rd93f02ec1a93401a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Costs" sheetId="7" r:id="Re5d9228aaff74e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Set" sheetId="1" r:id="R42148c01ad554e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Templates &amp; Global" sheetId="2" r:id="R8c2b5b02b0a241da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product &amp; Content" sheetId="3" r:id="R46c9e4a79eb24de6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions &amp; Access" sheetId="4" r:id="R790ca0f09bcb4ec8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Plan" sheetId="5" r:id="R68303009b960456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA &amp; Launch Gates" sheetId="6" r:id="Rfbd853e192e5453a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Costs" sheetId="7" r:id="R6e5c4df8829b4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Register" sheetId="8" r:id="Rbef768cf8ed14612"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training &amp; Handoff" sheetId="9" r:id="R12a935fa2696487c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Staging Packet" sheetId="10" r:id="R5c6213b83cdd4385"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +62,83 @@
       <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF166534"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF92400E"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1D4ED8"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF52645C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF195C3B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF111827"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF52645C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF425C50"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF155E3B"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF173F35"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF23463A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="26">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,14 +165,150 @@
         <x:fgColor rgb="FFE5E7EB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFEF3C7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDBEAFE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF195C3B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5E7EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFBFE6F4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF195C3B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5E7EB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCFCE7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF155E3B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEFF5E9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDE4E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC5E9F6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="7">
     <x:border/>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FF6DC5EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FF6DC5EA"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF6DC5EA"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="medium">
+        <x:color rgb="FF8AA79A"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD5E0DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD5E0DB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD5E0DB"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD5E0DB"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="121">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -139,18 +353,245 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="24" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="18" fillId="24" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="24" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="25">
+  <x:dxfs count="35">
     <x:dxf>
       <x:font>
         <x:b/>
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -161,7 +602,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -172,7 +613,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -183,7 +624,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -193,7 +634,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -204,7 +645,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -215,7 +656,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -226,7 +667,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -237,7 +678,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -247,7 +688,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -258,7 +699,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -269,7 +710,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -280,7 +721,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -291,7 +732,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -301,7 +742,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -312,7 +753,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -323,7 +764,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -334,7 +775,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -345,7 +786,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -355,7 +796,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -366,7 +807,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -377,7 +818,7 @@
         <x:color rgb="FF195C3B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EFD9"/>
         </x:patternFill>
       </x:fill>
@@ -388,7 +829,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -399,7 +840,7 @@
         <x:color rgb="FF6B501C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7E8B8"/>
         </x:patternFill>
       </x:fill>
@@ -409,8 +850,117 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF8D7DA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF6B501C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF6E8B1"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF195C3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD8EFD5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9F2940"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF6D1D5"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF195C3B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFD9EFD9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF6B501C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF7E8B8"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF842029"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFF8D7DA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF166534"/>
+      </x:font>
+      <x:fill>
         <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFF8D7DA"/>
+          <x:bgColor rgb="FFDCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF92400E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEF3C7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF991B1B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF3730A3"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE0E7FF"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -519,6 +1069,22 @@
     <x:tableColumn id="5" name="Trigger"/>
     <x:tableColumn id="6" name="Status"/>
     <x:tableColumn id="7" name="Source / Boundary"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PhaseTwoTrainingHandoff" displayName="PhaseTwoTrainingHandoff" ref="A5:H18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="#"/>
+    <x:tableColumn id="2" name="Welcome Packet Item"/>
+    <x:tableColumn id="3" name="What Staff Will Learn or Do"/>
+    <x:tableColumn id="4" name="Blue Nova Provides"/>
+    <x:tableColumn id="5" name="Client Provides or Does"/>
+    <x:tableColumn id="6" name="Timing / Gate"/>
+    <x:tableColumn id="7" name="Status"/>
+    <x:tableColumn id="8" name="Evidence / Link"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -750,31 +1316,30 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>In review</x:v>
+        <x:v>Internally approved</x:v>
       </x:c>
       <x:c r="D3" s="13" t="n">
-        <x:f>COUNTIF(E6:E12,"In review")</x:f>
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="F3" s="13" t="n">
         <x:f>COUNTIF(E6:E12,"Planned")+COUNTIF(E6:E12,"Planned next")</x:f>
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>Approved</x:v>
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="H3" s="13" t="n">
-        <x:f>COUNTIF(E6:E12,"Approved")</x:f>
+        <x:f>COUNTIF(E6:E12,"Client Approved")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="I3" s="9" t="str">
-        <x:v>Current gate</x:v>
+        <x:v>Current gates</x:v>
       </x:c>
       <x:c r="J3" s="13" t="str">
-        <x:v>Local approval</x:v>
+        <x:v>Client approval</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
@@ -823,7 +1388,7 @@
         <x:v>Sitewide</x:v>
       </x:c>
       <x:c r="E6" s="20" t="str">
-        <x:v>In review</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
         <x:v>Local mockup</x:v>
@@ -838,7 +1403,7 @@
         <x:v>Store entry, internal links, policy links, responsive navigation, account/cart indexation.</x:v>
       </x:c>
       <x:c r="J6" s="20" t="str">
-        <x:v>Approve before building the store homepage.</x:v>
+        <x:v>Exact Header + Footer Ecommerce Add-On v1.5 was approved by Todd on September 2, 2026 and is ready for Rebekah's separate client review. In the local review, the header, tablet, and footer Online Store links open Shop Homepage + Product Catalog v1.8; production will use the real /shop/ route. v1.4 remains preserved as superseded history.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="80" customHeight="1">
@@ -846,31 +1411,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="20" t="str">
-        <x:v>Online Store Homepage</x:v>
+        <x:v>Main Homepage Ecommerce Integration</x:v>
       </x:c>
       <x:c r="C7" s="20" t="str">
-        <x:v>Store introduction, Shop All path, category/brand/goal discovery, featured products, product-help guidance</x:v>
+        <x:v>All existing homepage components plus the Shop Online hero entry and one ecommerce section with three illustrated shopping paths and four featured product cards</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
-        <x:v>/online-store/ or approved store entry</x:v>
+        <x:v>/</x:v>
       </x:c>
       <x:c r="E7" s="20" t="str">
-        <x:v>Planned next</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Local page-body mockup</x:v>
       </x:c>
       <x:c r="G7" s="20" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H7" s="20" t="str">
-        <x:v>Separate from the main website homepage and the product archive. Rebuild the recovered early concept in the approved chrome.</x:v>
+        <x:v>Preserve every existing homepage component. Add only the Shop Online button and ecommerce section. Use broad-assortment language; omit Clarkston, fulfillment, shipping, and internal notes. Global chrome stays outside this page mockup.</x:v>
       </x:c>
       <x:c r="I7" s="20" t="str">
-        <x:v>Unique store landing copy, discovery paths, internal links, trust/help messaging, representative products.</x:v>
+        <x:v>Existing homepage SEO/content remains primary; add clear internal links to /shop/ and useful product discovery without internal mockup or integration language.</x:v>
       </x:c>
       <x:c r="J7" s="20" t="str">
-        <x:v>Approve before finalizing the archive hierarchy.</x:v>
+        <x:v>Exact Main Homepage Ecommerce Integration v1.9 was approved by Todd on September 2, 2026 and is ready for Rebekah's separate client review. The Shop Online hero entry opens the separate Shop Homepage + Product Catalog v1.8 preview instead of jumping to the homepage ecommerce section. Production will use /shop/. v1.8 is superseded without approval; any later design change requires v1.10 and a new approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="80" customHeight="1">
@@ -878,34 +1443,34 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="20" t="str">
-        <x:v>Shop + Catalog Template</x:v>
+        <x:v>Shop Homepage + Product Catalog</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>Shop All, category, brand, collection, search results, product cards, filters, sorting, pagination, no results</x:v>
+        <x:v>Store introduction, four approved illustrated wellness-goal paths, personal shopping guidance, catalog search, sort, filters, six sample products, pagination, no-results recovery, and the approved sitewide missing-product-photo component</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>/shop/ and shared archives</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Local page-body mockup</x:v>
       </x:c>
       <x:c r="G8" s="20" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H8" s="20" t="str">
-        <x:v>One reusable archive template; no separate one-off designs for every category, brand, collection, or search result.</x:v>
+        <x:v>Use /shop/ as both the store homepage and full catalog. Keep the customer-facing toolbar personal and helpful instead of emphasizing sample-product counts. Real product data still requires Revel/Kosmos validation.</x:v>
       </x:c>
       <x:c r="I8" s="20" t="str">
-        <x:v>Archive headings, breadcrumbs, canonicals, pagination, filter/indexation rules, card semantics.</x:v>
+        <x:v>Unique shop introduction, category discovery, archive headings, breadcrumbs, canonicals, pagination, filter/indexation rules, card semantics, accessible result feedback, and product-help content.</x:v>
       </x:c>
       <x:c r="J8" s="20" t="str">
-        <x:v>Approve before product-page work.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="80" customHeight="1">
+        <x:v>Exact Shop Homepage + Product Catalog v1.8 was approved by Todd on August 31, 2026 and is ready for Rebekah's separate client review. This visual approval includes the page structure, wellness paths, personal messaging, benefits/help row, product cards, search, sorting, filters, load-more, no-results recovery, and sitewide missing-photo component. Revel/Kosmos data, synchronization, inventory, pricing, categories, real photography, and final product content remain separate implementation-validation gates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="84" hidden="0" customHeight="1">
       <x:c r="A9" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -913,28 +1478,28 @@
         <x:v>Product Page Templates</x:v>
       </x:c>
       <x:c r="C9" s="20" t="str">
-        <x:v>Simple product and variation product examples</x:v>
+        <x:v>Simple and variation product examples with three-view galleries, the approved sitewide missing-product-photo component, quantity and variation controls, compact product details, optional source-verified Directions &amp; Warnings, phone help beside Add to Cart, and related products</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>/product/{slug}/</x:v>
       </x:c>
       <x:c r="E9" s="20" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F9" s="20" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Local page-body mockup</x:v>
       </x:c>
       <x:c r="G9" s="20" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H9" s="20" t="str">
-        <x:v>Two approval examples share one system. Final fields wait for the first Revel/Kosmos product. Reviews and unsupported claims are excluded.</x:v>
+        <x:v>Approve the shared structure and interactions now. Directions &amp; Warnings is collapsed and appears only when verified packaging, manufacturer/supplier materials, or approved catalog data exists; otherwise omit it. Shipping and returns stay in the purchase path and policy pages. Product media and connected catalog content still wait for Revel/Kosmos.</x:v>
       </x:c>
       <x:c r="I9" s="20" t="str">
-        <x:v>Product schema, unique copy, gallery, facts, cautions, stock, shipping note, variation errors, related items.</x:v>
+        <x:v>Product schema, unique copy, gallery semantics and alt text, compact product details, source-verified directions/warnings when applicable, stock language, variation errors, related items, and accessible support information.</x:v>
       </x:c>
       <x:c r="J9" s="20" t="str">
-        <x:v>Approve both examples before the purchase path.</x:v>
+        <x:v>Exact Product Page Templates v1.7 was approved by Todd on August 31, 2026 and is ready for Rebekah's separate client review. Approval covers both product examples, galleries, the approved missing-photo treatment, quantity and variation controls, compact details, optional source-verified Directions &amp; Warnings, phone guidance near Add to Cart, and related products. Revel/Kosmos data and verified manufacturer, supplier, label, or approved-catalog content remain separate implementation-validation gates.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="80" customHeight="1">
@@ -945,31 +1510,31 @@
         <x:v>Purchase Path</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
-        <x:v>Cart, empty cart, checkout, validation, order confirmation</x:v>
+        <x:v>Connected cart with the approved sitewide missing-product-photo component, empty-cart recovery, checkout fields, validation, order review, and customer-facing confirmation</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
         <x:v>/cart/; /checkout/; confirmation</x:v>
       </x:c>
       <x:c r="E10" s="20" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F10" s="20" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Local page-body mockup</x:v>
       </x:c>
       <x:c r="G10" s="20" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H10" s="20" t="str">
-        <x:v>One connected prototype. Shipping, tax, payment, and failure specifics remain provisional until approved services are available.</x:v>
+        <x:v>Approve the journey hierarchy and interactions now. Shipping rates, tax, payment fields, wallet options, provider messages, emails, and final totals wait for approved services and testing. Customer-facing copy must remain free of location and internal-review terminology.</x:v>
       </x:c>
       <x:c r="I10" s="20" t="str">
-        <x:v>Transactional indexation, clear policy/help links, consent, field labels, useful validation and recovery.</x:v>
+        <x:v>Transactional indexation, policy and help links, consent, field labels, validation, recovery, order status, and customer support information.</x:v>
       </x:c>
       <x:c r="J10" s="20" t="str">
-        <x:v>Approve the complete cart-to-confirmation journey.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="80" customHeight="1">
+        <x:v>Exact Purchase Path v1.6 was approved by Todd on August 31, 2026 and is ready for Rebekah's separate client review. Approval covers the cart, approved missing-photo cart treatment, empty-cart recovery, guest-checkout fields, validation, order review, customer-facing confirmation, and representative interactions. Live payment fields and failures, shipping rates, tax calculations, wallet options, fraud rules, transactional emails, inventory and order synchronization, final totals, and provider messages remain separate connected-service and Revel/Kosmos validation gates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="96" hidden="0" customHeight="1">
       <x:c r="A11" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -977,28 +1542,28 @@
         <x:v>Customer Account System</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
-        <x:v>Login, optional registration, password reset, dashboard, addresses, order history, order detail</x:v>
+        <x:v>Guest checkout, automatic optional account creation, sign-in, password recovery, dashboard, addresses, order history, order detail, and clearly separated review guidance</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:v>/my-account/ and child screens</x:v>
       </x:c>
       <x:c r="E11" s="20" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F11" s="20" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Local page-body mockup</x:v>
       </x:c>
       <x:c r="G11" s="20" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="H11" s="20" t="str">
-        <x:v>One reusable account shell. Guest checkout with optional accounts remains proposed until client approval.</x:v>
+        <x:v>Approve the customer experience now: guest checkout stays available during checkout; customers create optional accounts without staff approval; standard email, password, and recovery are used; customer 2FA is not planned. Staff/administrator backend security is configured and tested separately before launch.</x:v>
       </x:c>
       <x:c r="I11" s="20" t="str">
-        <x:v>Noindex account screens, privacy/consent, password recovery, order and address clarity.</x:v>
+        <x:v>Noindex account screens; privacy and consent; standard sign-in and password recovery, clear field labels, order access, address editing, and customer-safe support guidance.</x:v>
       </x:c>
       <x:c r="J11" s="20" t="str">
-        <x:v>Approve after purchase-path rules are settled.</x:v>
+        <x:v>Exact Customer Account System v1.6 was approved by Todd on September 1, 2026 and is ready for Rebekah's separate client review. Approval covers guest checkout, automatic optional account creation, standard email/password sign-in and recovery, dashboard, addresses, order history, order detail, representative interactions, and no customer 2FA. Staff/administrator backend security remains a separate staging task, and real email delivery, privacy/consent wording, order synchronization, and retention behavior remain implementation-validation gates.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="80" customHeight="1">
@@ -1009,28 +1574,28 @@
         <x:v>Store States + Components</x:v>
       </x:c>
       <x:c r="C12" s="20" t="str">
-        <x:v>No results, filter empty, out of stock, unavailable variation, missing image, loading, cart empty, validation/errors, mobile filter</x:v>
+        <x:v>Ten non-ideal states including the approved sitewide missing-product-photo component and its usage rule, plus the mobile filter dialog and responsive/accessibility checklist</x:v>
       </x:c>
       <x:c r="D12" s="20" t="str">
         <x:v>Shared across store</x:v>
       </x:c>
       <x:c r="E12" s="20" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Internally Approved</x:v>
       </x:c>
       <x:c r="F12" s="20" t="str">
-        <x:v>Not started</x:v>
+        <x:v>Local page-body mockup</x:v>
       </x:c>
       <x:c r="G12" s="20" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H12" s="20" t="str">
-        <x:v>Approve non-ideal states and run desktop, tablet, phone, keyboard, focus, contrast, labels, and reduced-motion review across all systems.</x:v>
+        <x:v>Approve recovery hierarchy and accessibility behavior now. The missing-product-photo component is an approved site rule: use it only in real product-photo slots lacking approved photography, then replace it automatically when photography arrives.</x:v>
       </x:c>
       <x:c r="I12" s="20" t="str">
-        <x:v>Honest stock/error language, accessible recovery actions, complete responsive behavior.</x:v>
+        <x:v>Honest stock/error language, accessible recovery actions, complete responsive behavior, keyboard/focus, labels, contrast, and reduced motion.</x:v>
       </x:c>
       <x:c r="J12" s="20" t="str">
-        <x:v>Final design-system QA and client approval.</x:v>
+        <x:v>Exact Store States + Components v1.5 was approved by Todd on September 1, 2026 and is ready for Rebekah's separate client review. Approval covers all ten states, recovery actions, the approved sitewide missing-product-photo rule, loading treatment, mobile filter drawer, and responsive/accessibility checklist. Exact inventory, shipping, tax, payment-provider, authentication, and integration-error messages remain connected-service implementation-validation gates.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1047,7 +1612,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="E6:E30">
-      <x:formula1>"Planned,Planned next,In review,Revision needed,Approved"</x:formula1>
+      <x:formula1>"Planned,Planned next,In review,Revision needed,Internally Approved,Client Approved"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F6:F30">
       <x:formula1>"Not started,Local mockup,Local prototype,Approved for build,Implemented"</x:formula1>
@@ -1058,8 +1623,408 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red8d2f3ab12b4c45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8533d231fb98460a"/>
   </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="92" t="str">
+        <x:v>Phase Two Local Readiness and Pre-Staging Packet</x:v>
+      </x:c>
+      <x:c r="B1" s="92"/>
+      <x:c r="C1" s="92"/>
+      <x:c r="D1" s="92"/>
+      <x:c r="E1" s="92"/>
+      <x:c r="F1" s="92"/>
+      <x:c r="G1" s="92"/>
+      <x:c r="H1" s="92"/>
+    </x:row>
+    <x:row r="2" ht="44" customHeight="1">
+      <x:c r="A2" s="96" t="str">
+        <x:v>Local work only. No Cloudways, staging, live website, WordPress deployment, Revel/Kosmos connection, purchase, subscription, or paid-service action is authorized by this sheet.</x:v>
+      </x:c>
+      <x:c r="B2" s="96"/>
+      <x:c r="C2" s="96"/>
+      <x:c r="D2" s="96"/>
+      <x:c r="E2" s="96"/>
+      <x:c r="F2" s="96"/>
+      <x:c r="G2" s="96"/>
+      <x:c r="H2" s="96"/>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="98" t="str">
+        <x:v>Tracked</x:v>
+      </x:c>
+      <x:c r="B3" s="98" t="n">
+        <x:f>COUNTA(A6:A16)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="98" t="str">
+        <x:v>Local complete</x:v>
+      </x:c>
+      <x:c r="D3" s="98" t="n">
+        <x:f>COUNTIF(C6:C16,"Local complete")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E3" s="98" t="str">
+        <x:v>Pending client</x:v>
+      </x:c>
+      <x:c r="F3" s="98" t="n">
+        <x:f>COUNTIF(C6:C16,"Pending client")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="98" t="str">
+        <x:v>Gated later</x:v>
+      </x:c>
+      <x:c r="H3" s="98" t="n">
+        <x:f>COUNTIF(C6:C16,"External gate")+COUNTIF(C6:C16,"Future gated")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="103" t="str">
+        <x:v>Order</x:v>
+      </x:c>
+      <x:c r="B5" s="103" t="str">
+        <x:v>Work Package</x:v>
+      </x:c>
+      <x:c r="C5" s="103" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="D5" s="103" t="str">
+        <x:v>Current Boundary</x:v>
+      </x:c>
+      <x:c r="E5" s="103" t="str">
+        <x:v>Ready Evidence</x:v>
+      </x:c>
+      <x:c r="F5" s="103" t="str">
+        <x:v>Next Gate</x:v>
+      </x:c>
+      <x:c r="G5" s="103" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="H5" s="103" t="str">
+        <x:v>Local Document / Record</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="66" customHeight="1">
+      <x:c r="A6" s="115" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="114" t="str">
+        <x:v>Exact mockup approval set</x:v>
+      </x:c>
+      <x:c r="C6" s="114" t="str">
+        <x:v>Pending client</x:v>
+      </x:c>
+      <x:c r="D6" s="114" t="str">
+        <x:v>All seven systems are internally approved and frozen.</x:v>
+      </x:c>
+      <x:c r="E6" s="114" t="str">
+        <x:v>Review hub and version register show the exact current versions.</x:v>
+      </x:c>
+      <x:c r="F6" s="114" t="str">
+        <x:v>Rebekah approves all seven exact versions or requests a numbered revision.</x:v>
+      </x:c>
+      <x:c r="G6" s="114" t="str">
+        <x:v>Todd / Rebekah</x:v>
+      </x:c>
+      <x:c r="H6" s="114" t="str">
+        <x:v>phase-two-ecommerce-mockup-sheet.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="66" customHeight="1">
+      <x:c r="A7" s="116" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="112" t="str">
+        <x:v>Pre-staging execution and rollback runbook</x:v>
+      </x:c>
+      <x:c r="C7" s="112" t="str">
+        <x:v>Local complete</x:v>
+      </x:c>
+      <x:c r="D7" s="112" t="str">
+        <x:v>Planning only; no server or staging action.</x:v>
+      </x:c>
+      <x:c r="E7" s="112" t="str">
+        <x:v>Gates, safeguards, evidence requirements, deployment rule, and rollback levels are written.</x:v>
+      </x:c>
+      <x:c r="F7" s="112" t="str">
+        <x:v>Use only after client approval, access verification, a safe window, and Todd authorization.</x:v>
+      </x:c>
+      <x:c r="G7" s="112" t="str">
+        <x:v>Blue Nova</x:v>
+      </x:c>
+      <x:c r="H7" s="112" t="str">
+        <x:v>PHASE-TWO-PRE-STAGING-EXECUTION-RUNBOOK-v1.1.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="66" customHeight="1">
+      <x:c r="A8" s="118" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="117" t="str">
+        <x:v>One-product synchronization acceptance test</x:v>
+      </x:c>
+      <x:c r="C8" s="117" t="str">
+        <x:v>Local complete</x:v>
+      </x:c>
+      <x:c r="D8" s="117" t="str">
+        <x:v>Test definition only; no connection.</x:v>
+      </x:c>
+      <x:c r="E8" s="117" t="str">
+        <x:v>Preflight, field observation, overwrite, order, inventory, and pass/fail checks are written.</x:v>
+      </x:c>
+      <x:c r="F8" s="117" t="str">
+        <x:v>Populate with observed values during the first authorized staging pull.</x:v>
+      </x:c>
+      <x:c r="G8" s="117" t="str">
+        <x:v>Blue Nova / Mark</x:v>
+      </x:c>
+      <x:c r="H8" s="117" t="str">
+        <x:v>PHASE-TWO-ONE-PRODUCT-ACCEPTANCE-TEST-v1.1.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="66" customHeight="1">
+      <x:c r="A9" s="116" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="112" t="str">
+        <x:v>Legacy catalog clean-start plan</x:v>
+      </x:c>
+      <x:c r="C9" s="112" t="str">
+        <x:v>Local complete</x:v>
+      </x:c>
+      <x:c r="D9" s="112" t="str">
+        <x:v>No production catalog change and no deletion.</x:v>
+      </x:c>
+      <x:c r="E9" s="112" t="str">
+        <x:v>Quarantine, collision, reconciliation, evidence, and rollback rules are written.</x:v>
+      </x:c>
+      <x:c r="F9" s="112" t="str">
+        <x:v>Execute only on protected staging before the first product pull.</x:v>
+      </x:c>
+      <x:c r="G9" s="112" t="str">
+        <x:v>Blue Nova</x:v>
+      </x:c>
+      <x:c r="H9" s="112" t="str">
+        <x:v>PHASE-TWO-LEGACY-CATALOG-CLEAN-START-PLAN-v1.1.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="66" customHeight="1">
+      <x:c r="A10" s="118" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="117" t="str">
+        <x:v>Ecommerce policy decision draft</x:v>
+      </x:c>
+      <x:c r="C10" s="117" t="str">
+        <x:v>Local complete</x:v>
+      </x:c>
+      <x:c r="D10" s="117" t="str">
+        <x:v>Internal draft; not legal advice or approved website copy.</x:v>
+      </x:c>
+      <x:c r="E10" s="117" t="str">
+        <x:v>Confirmed operating facts and unresolved shipping/return/cancellation/damage decisions are separated.</x:v>
+      </x:c>
+      <x:c r="F10" s="117" t="str">
+        <x:v>Rebekah answers the focused decisions; final wording is approved before launch.</x:v>
+      </x:c>
+      <x:c r="G10" s="117" t="str">
+        <x:v>Rebekah / qualified reviewer</x:v>
+      </x:c>
+      <x:c r="H10" s="117" t="str">
+        <x:v>PHASE-TWO-ECOMMERCE-POLICY-DECISION-DRAFT-v1.1.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="66" customHeight="1">
+      <x:c r="A11" s="116" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" s="112" t="str">
+        <x:v>Dormant WooCommerce theme scaffold</x:v>
+      </x:c>
+      <x:c r="C11" s="112" t="str">
+        <x:v>Local complete</x:v>
+      </x:c>
+      <x:c r="D11" s="112" t="str">
+        <x:v>Files exist locally but are not loaded, deployed, or activated.</x:v>
+      </x:c>
+      <x:c r="E11" s="112" t="str">
+        <x:v>Guarded PHP, scoped CSS, accessible filter-drawer JS, utility/footer renderers, and approved fallback component exist.</x:v>
+      </x:c>
+      <x:c r="F11" s="112" t="str">
+        <x:v>Activate on protected staging only after exact client approval and version inspection.</x:v>
+      </x:c>
+      <x:c r="G11" s="112" t="str">
+        <x:v>Blue Nova</x:v>
+      </x:c>
+      <x:c r="H11" s="112" t="str">
+        <x:v>wordpress/theme/rebekahs-2026/PHASE-TWO-ECOMMERCE-SCAFFOLD-v1.1.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="66" customHeight="1">
+      <x:c r="A12" s="118" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="117" t="str">
+        <x:v>Access and working-window verification</x:v>
+      </x:c>
+      <x:c r="C12" s="117" t="str">
+        <x:v>External gate</x:v>
+      </x:c>
+      <x:c r="D12" s="117" t="str">
+        <x:v>No external login during local preparation.</x:v>
+      </x:c>
+      <x:c r="E12" s="117" t="str">
+        <x:v>Revel invite and client-owned Kosmos account are recorded; operational permissions and timing remain unverified.</x:v>
+      </x:c>
+      <x:c r="F12" s="117" t="str">
+        <x:v>Verify Clarkston Revel permissions, Kosmos access/trial timing, one prepared product, and the working window.</x:v>
+      </x:c>
+      <x:c r="G12" s="117" t="str">
+        <x:v>Todd / Rebekah / Blue Nova</x:v>
+      </x:c>
+      <x:c r="H12" s="117" t="str">
+        <x:v>PHASE-TWO-MASTER-CHECKLIST.md sections 1, 2, and 5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="66" customHeight="1">
+      <x:c r="A13" s="116" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="112" t="str">
+        <x:v>Protected staging and restore point</x:v>
+      </x:c>
+      <x:c r="C13" s="112" t="str">
+        <x:v>Future gated</x:v>
+      </x:c>
+      <x:c r="D13" s="112" t="str">
+        <x:v>No independent staging exists and no server action is authorized.</x:v>
+      </x:c>
+      <x:c r="E13" s="112" t="str">
+        <x:v>Runbook defines the required safety evidence.</x:v>
+      </x:c>
+      <x:c r="F13" s="112" t="str">
+        <x:v>Todd authorizes server scale, restore point, and staging creation after prerequisites are ready.</x:v>
+      </x:c>
+      <x:c r="G13" s="112" t="str">
+        <x:v>Blue Nova</x:v>
+      </x:c>
+      <x:c r="H13" s="112" t="str">
+        <x:v>Runbook gates 2–4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="66" customHeight="1">
+      <x:c r="A14" s="118" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="117" t="str">
+        <x:v>One-product Revel/Kosmos/WooCommerce proof</x:v>
+      </x:c>
+      <x:c r="C14" s="117" t="str">
+        <x:v>Future gated</x:v>
+      </x:c>
+      <x:c r="D14" s="117" t="str">
+        <x:v>No connection or field mapping has been performed.</x:v>
+      </x:c>
+      <x:c r="E14" s="117" t="str">
+        <x:v>Acceptance test is ready for actual values.</x:v>
+      </x:c>
+      <x:c r="F14" s="117" t="str">
+        <x:v>Protected staging and connection prerequisites pass.</x:v>
+      </x:c>
+      <x:c r="G14" s="117" t="str">
+        <x:v>Blue Nova / Kosmos / Revel</x:v>
+      </x:c>
+      <x:c r="H14" s="117" t="str">
+        <x:v>Acceptance test v1.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="66" customHeight="1">
+      <x:c r="A15" s="116" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="112" t="str">
+        <x:v>Remaining 24 products and real storefront</x:v>
+      </x:c>
+      <x:c r="C15" s="112" t="str">
+        <x:v>Future gated</x:v>
+      </x:c>
+      <x:c r="D15" s="112" t="str">
+        <x:v>No bulk pull, taxonomy finalization, or content polishing.</x:v>
+      </x:c>
+      <x:c r="E15" s="112" t="str">
+        <x:v>Approved designs and clean-start rules are ready.</x:v>
+      </x:c>
+      <x:c r="F15" s="112" t="str">
+        <x:v>One-product test passes and exact transfer/overwrite behavior is documented.</x:v>
+      </x:c>
+      <x:c r="G15" s="112" t="str">
+        <x:v>Blue Nova / Mark / Rebekah</x:v>
+      </x:c>
+      <x:c r="H15" s="112" t="str">
+        <x:v>Master checklist sections 3, 4, 6, and 8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="66" customHeight="1">
+      <x:c r="A16" s="120" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="119" t="str">
+        <x:v>QA, client signoff, training, launch, stabilization</x:v>
+      </x:c>
+      <x:c r="C16" s="119" t="str">
+        <x:v>Future gated</x:v>
+      </x:c>
+      <x:c r="D16" s="119" t="str">
+        <x:v>No public store or transaction activity.</x:v>
+      </x:c>
+      <x:c r="E16" s="119" t="str">
+        <x:v>Twenty-eight launch tests and thirteen handoff items remain tracked in the workbook.</x:v>
+      </x:c>
+      <x:c r="F16" s="119" t="str">
+        <x:v>Every applicable QA test passes and Rebekah authorizes controlled launch.</x:v>
+      </x:c>
+      <x:c r="G16" s="119" t="str">
+        <x:v>Blue Nova / Rebekah</x:v>
+      </x:c>
+      <x:c r="H16" s="119" t="str">
+        <x:v>QA &amp; Launch Gates; Training &amp; Handoff</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="C6:C16">
+    <x:cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="Local complete"/>
+    <x:cfRule type="containsText" dxfId="32" priority="2" operator="containsText" text="Pending client"/>
+    <x:cfRule type="containsText" dxfId="33" priority="3" operator="containsText" text="External gate"/>
+    <x:cfRule type="containsText" dxfId="34" priority="4" operator="containsText" text="Future gated"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="C6:C16">
+      <x:formula1>"Local complete,Pending client,External gate,Future gated"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -1152,7 +2117,7 @@
         <x:v>Image, name, brand/category context, price placeholder, stock/sale state, and accessible action. No reviews or wishlist.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="64" customHeight="1">
+    <x:row r="8" ht="48" hidden="0" customHeight="1">
       <x:c r="A8" s="20" t="str">
         <x:v>Template</x:v>
       </x:c>
@@ -1166,10 +2131,10 @@
         <x:v>Approve example</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>Gallery, facts, price/stock placeholders, quantity, add to cart, cautions, shipping note, related products.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="64" customHeight="1">
+        <x:v>Gallery, compact product details, price/stock placeholders, quantity, add to cart, phone guidance, related products, and a collapsed Directions &amp; Warnings disclosure only when verified source content exists. Shipping and returns remain in the purchase path and policy pages.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
       <x:c r="A9" s="20" t="str">
         <x:v>Template</x:v>
       </x:c>
@@ -1183,7 +2148,7 @@
         <x:v>Approve example</x:v>
       </x:c>
       <x:c r="E9" s="20" t="str">
-        <x:v>Reuse simple layout with option selection, availability, price changes, unavailable combinations, and errors.</x:v>
+        <x:v>Reuse the simple layout and the same optional content rules with option selection, availability, price changes, unavailable combinations, and errors.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
@@ -1203,7 +2168,7 @@
         <x:v>One customer journey with empty cart, validation, policy/help links, and confirmation—not unrelated pages.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="64" customHeight="1">
+    <x:row r="11" ht="48" hidden="0" customHeight="1">
       <x:c r="A11" s="20" t="str">
         <x:v>Template</x:v>
       </x:c>
@@ -1211,13 +2176,13 @@
         <x:v>Customer account shell</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
-        <x:v>Login, registration, reset, dashboard, addresses, and orders</x:v>
+        <x:v>Login, optional registration, password reset, dashboard, addresses, and orders</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
-        <x:v>Approve representative states</x:v>
+        <x:v>Approve representative states, guest checkout, and optional-account presentation</x:v>
       </x:c>
       <x:c r="E11" s="20" t="str">
-        <x:v>One compact shell; optional accounts remain provisional until approved.</x:v>
+        <x:v>One compact customer shell. Guest checkout remains available during checkout; optional customer accounts are automatic and use the standard email, password, and reset flow. No customer 2FA add-on is planned. Staff/administrator backend protection is handled separately.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
@@ -1231,7 +2196,7 @@
         <x:v>Catalog, product, cart, checkout, and account</x:v>
       </x:c>
       <x:c r="D12" s="20" t="str">
-        <x:v>Approve component sheet</x:v>
+        <x:v>Internally approved; client approval pending</x:v>
       </x:c>
       <x:c r="E12" s="20" t="str">
         <x:v>No results, stock/variation, missing image, loading, cart empty, validation, payment placeholder, and mobile filter states.</x:v>
@@ -1248,7 +2213,7 @@
         <x:v>Sitewide</x:v>
       </x:c>
       <x:c r="D13" s="20" t="str">
-        <x:v>Current review item</x:v>
+        <x:v>Internally approved; awaiting client</x:v>
       </x:c>
       <x:c r="E13" s="20" t="str">
         <x:v>Approved Phase One header plus Online Store, search, My Account, and cart/count. Do not redesign original navigation.</x:v>
@@ -1265,7 +2230,7 @@
         <x:v>Sitewide footer</x:v>
       </x:c>
       <x:c r="D14" s="20" t="str">
-        <x:v>Current review item</x:v>
+        <x:v>Internally approved; awaiting client</x:v>
       </x:c>
       <x:c r="E14" s="20" t="str">
         <x:v>Add one fifth expandable section while preserving original footer and accordion behavior.</x:v>
@@ -1354,6 +2319,23 @@
       </x:c>
       <x:c r="E19" s="20" t="str">
         <x:v>Search, product view, add to cart, checkout start, purchase, errors, and consent-aware tracking.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="108" customHeight="1">
+      <x:c r="A20" s="85" t="str">
+        <x:v>Component</x:v>
+      </x:c>
+      <x:c r="B20" s="85" t="str">
+        <x:v>Missing product photo placeholder</x:v>
+      </x:c>
+      <x:c r="C20" s="85" t="str">
+        <x:v>Catalog cards, product galleries, related products, cart items, and store-state examples</x:v>
+      </x:c>
+      <x:c r="D20" s="85" t="str">
+        <x:v>Approved site rule; client sees exact component in Store States v1.5</x:v>
+      </x:c>
+      <x:c r="E20" s="85" t="str">
+        <x:v>Use Rebekah's upright green-and-honey brand mark, warm honey/sage treatment, and 'Product photo coming soon.' Replace it automatically when approved photography arrives. Do not use it for loading, broken-image errors, decorative imagery, or content never intended to have a photo. Build one reusable WordPress component rather than redesigning it page by page.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1368,7 +2350,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12d1bb5032c74a29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e7a53d8dcc4383"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1410,14 +2392,14 @@
       </x:c>
       <x:c r="D3" s="13" t="n">
         <x:f>COUNTIF(F6:F24,"Pending access")+COUNTIF(F6:F24,"Pending product data")+COUNTIF(F6:F24,"Pending pilot data")+COUNTIF(F6:F24,"Pending sync test")</x:f>
-        <x:v>18</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
         <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="F3" s="13" t="n">
         <x:f>COUNTIF(F6:F24,"Confirmed")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
         <x:v>Pilot size</x:v>
@@ -1468,14 +2450,14 @@
       <x:c r="E6" s="20" t="str">
         <x:v>Rebekah / Mark</x:v>
       </x:c>
-      <x:c r="F6" s="20" t="str">
-        <x:v>Pending product data</x:v>
+      <x:c r="F6" s="32" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="G6" s="20" t="str">
-        <x:v>Only intended pilot products appear online.</x:v>
+        <x:v>All 25 export rows show Active = Yes and Display on online/third-party = Yes.</x:v>
       </x:c>
       <x:c r="H6" s="20" t="str">
-        <x:v>Confirm Clarkston establishment eligibility.</x:v>
+        <x:v>They are eligible to pull; the first Kosmos test still must prove that all 25 arrive.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -1494,14 +2476,14 @@
       <x:c r="E7" s="20" t="str">
         <x:v>Rebekah / Mark</x:v>
       </x:c>
-      <x:c r="F7" s="20" t="str">
-        <x:v>Pending product data</x:v>
+      <x:c r="F7" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="G7" s="20" t="str">
-        <x:v>No register shorthand; variation parent name is consistent.</x:v>
+        <x:v>All 25 names are present; customer-facing capitalization and wording still need review.</x:v>
       </x:c>
       <x:c r="H7" s="20" t="str">
-        <x:v>Must survive synchronization.</x:v>
+        <x:v>The export uses register-style, mostly all-capital names.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
@@ -1520,14 +2502,14 @@
       <x:c r="E8" s="20" t="str">
         <x:v>Rebekah / Mark</x:v>
       </x:c>
-      <x:c r="F8" s="20" t="str">
-        <x:v>Pending product data</x:v>
+      <x:c r="F8" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="G8" s="20" t="str">
-        <x:v>No reused identifier across products or variations.</x:v>
+        <x:v>All 25 have distinct barcodes, but the SKU column is blank; confirm the integration key.</x:v>
       </x:c>
       <x:c r="H8" s="20" t="str">
-        <x:v>Primary reconciliation key.</x:v>
+        <x:v>Do not assume a blank SKU is acceptable until the first Kosmos mapping test.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
@@ -1546,14 +2528,14 @@
       <x:c r="E9" s="20" t="str">
         <x:v>Rebekah / Mark</x:v>
       </x:c>
-      <x:c r="F9" s="20" t="str">
-        <x:v>Pending product data</x:v>
+      <x:c r="F9" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="G9" s="20" t="str">
-        <x:v>Website price matches Revel after update.</x:v>
+        <x:v>All 25 prices are present in the export and must match after synchronization.</x:v>
       </x:c>
       <x:c r="H9" s="20" t="str">
-        <x:v>Test overwrite behavior.</x:v>
+        <x:v>Verify with the first pull and one update test.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
@@ -1579,10 +2561,10 @@
         <x:v>Nonnegative quantity; order reduces Clarkston only.</x:v>
       </x:c>
       <x:c r="H10" s="20" t="str">
-        <x:v>Validate buffer/backorder rules.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="62" customHeight="1">
+        <x:v>Clarkston inventory quantities and stock status are not included in this export.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="72" customHeight="1">
       <x:c r="A11" s="20" t="str">
         <x:v>Shipping</x:v>
       </x:c>
@@ -1590,7 +2572,7 @@
         <x:v>Accurate weight; dimensions for exceptions</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
-        <x:v>Revel</x:v>
+        <x:v>Revel if supported; otherwise WooCommerce</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:v>USPS live rates</x:v>
@@ -1602,10 +2584,10 @@
         <x:v>Pending product data</x:v>
       </x:c>
       <x:c r="G11" s="20" t="str">
-        <x:v>Representative carts return valid rates.</x:v>
+        <x:v>Representative carts return valid rates without relying on one unverified live weight.</x:v>
       </x:c>
       <x:c r="H11" s="20" t="str">
-        <x:v>Blue Nova configures packing; client flags bulky items.</x:v>
+        <x:v>No weight field appears in the export. A staging-only placeholder may be used; live rates require verified product weights.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -1624,14 +2606,14 @@
       <x:c r="E12" s="20" t="str">
         <x:v>Rebekah / Blue Nova</x:v>
       </x:c>
-      <x:c r="F12" s="20" t="str">
-        <x:v>Pending product data</x:v>
+      <x:c r="F12" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="G12" s="20" t="str">
-        <x:v>Duplicates and spelling variants reconciled.</x:v>
+        <x:v>Class, category, and subcategory are present for all 25; map them after the first pull.</x:v>
       </x:c>
       <x:c r="H12" s="20" t="str">
-        <x:v>Website taxonomy may differ.</x:v>
+        <x:v>Website categories may be simplified after import.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
@@ -1650,14 +2632,14 @@
       <x:c r="E13" s="20" t="str">
         <x:v>Rebekah / Mark</x:v>
       </x:c>
-      <x:c r="F13" s="20" t="str">
-        <x:v>Pending product data</x:v>
+      <x:c r="F13" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="G13" s="20" t="str">
-        <x:v>Consistent approved brand label.</x:v>
+        <x:v>Vendor is Rebekahs Private Label for all 25; confirm the customer-facing brand label.</x:v>
       </x:c>
       <x:c r="H13" s="20" t="str">
-        <x:v>Map after first import.</x:v>
+        <x:v>Test whether vendor/brand transfers through Kosmos.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
@@ -1709,10 +2691,10 @@
         <x:v>Approved, high quality, correct product, usable alt text.</x:v>
       </x:c>
       <x:c r="H15" s="20" t="str">
-        <x:v>Do not polish before overwrite behavior is known.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="62" customHeight="1">
+        <x:v>The export contains no product-image fields. Todd approved the catalog v1.8 treatment as the sitewide rule: the upright Rebekah green-and-honey mark, warm honey/sage treatment, and 'Product photo coming soon.' Use it only for genuine product-photo slots without approved photography; replace it automatically when approved photography arrives. Real photography still requires source confirmation and acceptance.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="72" customHeight="1">
       <x:c r="A16" s="20" t="str">
         <x:v>Content</x:v>
       </x:c>
@@ -1729,13 +2711,13 @@
         <x:v>Blue Nova / Rebekah</x:v>
       </x:c>
       <x:c r="F16" s="20" t="str">
-        <x:v>Pending sync test</x:v>
+        <x:v>Pending product data</x:v>
       </x:c>
       <x:c r="G16" s="20" t="str">
-        <x:v>Accurate, original, claims-safe, approved.</x:v>
+        <x:v>The Product Description field is blank for all 25 products.</x:v>
       </x:c>
       <x:c r="H16" s="20" t="str">
-        <x:v>Authorized manufacturer sources first.</x:v>
+        <x:v>Add approved customer-facing copy only after confirming field ownership and overwrite behavior.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="62" customHeight="1">
@@ -1764,7 +2746,7 @@
         <x:v>Where applicable.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="62" customHeight="1">
+    <x:row r="18" ht="24" hidden="0" customHeight="1">
       <x:c r="A18" s="20" t="str">
         <x:v>Compliance</x:v>
       </x:c>
@@ -1772,25 +2754,25 @@
         <x:v>Directions and serving information</x:v>
       </x:c>
       <x:c r="C18" s="20" t="str">
-        <x:v>WordPress / approved source</x:v>
+        <x:v>WordPress from approved label, manufacturer, or supplier source</x:v>
       </x:c>
       <x:c r="D18" s="20" t="str">
-        <x:v>Product detail</x:v>
+        <x:v>Product detail when applicable</x:v>
       </x:c>
       <x:c r="E18" s="20" t="str">
         <x:v>Blue Nova / Rebekah</x:v>
       </x:c>
       <x:c r="F18" s="20" t="str">
-        <x:v>Pending product data</x:v>
+        <x:v>Pending source validation</x:v>
       </x:c>
       <x:c r="G18" s="20" t="str">
-        <x:v>Matches approved label/source.</x:v>
+        <x:v>Publish only when verified source information is available; otherwise omit the section.</x:v>
       </x:c>
       <x:c r="H18" s="20" t="str">
-        <x:v>No invented guidance.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="62" customHeight="1">
+        <x:v>No invented guidance. Display as a collapsed Directions &amp; Warnings disclosure when applicable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="20" t="str">
         <x:v>Compliance</x:v>
       </x:c>
@@ -1816,7 +2798,7 @@
         <x:v>Use approved assets/data.</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="62" customHeight="1">
+    <x:row r="20" ht="36" hidden="0" customHeight="1">
       <x:c r="A20" s="20" t="str">
         <x:v>Compliance</x:v>
       </x:c>
@@ -1824,22 +2806,22 @@
         <x:v>Warnings, restrictions, shipping eligibility</x:v>
       </x:c>
       <x:c r="C20" s="20" t="str">
-        <x:v>WordPress / Revel flag</x:v>
+        <x:v>WordPress / Revel flag / approved source</x:v>
       </x:c>
       <x:c r="D20" s="20" t="str">
-        <x:v>Product and checkout</x:v>
+        <x:v>Product and checkout when applicable</x:v>
       </x:c>
       <x:c r="E20" s="20" t="str">
         <x:v>Rebekah / Blue Nova</x:v>
       </x:c>
       <x:c r="F20" s="20" t="str">
-        <x:v>Pending product data</x:v>
+        <x:v>Pending source validation</x:v>
       </x:c>
       <x:c r="G20" s="20" t="str">
-        <x:v>Known restrictions are visible and enforced.</x:v>
+        <x:v>Verified product-specific warnings and restrictions are visible where they apply and enforced when needed.</x:v>
       </x:c>
       <x:c r="H20" s="20" t="str">
-        <x:v>Routine products assumed shippable until exceptions identified.</x:v>
+        <x:v>Do not show a generic warning block on every product; omit it when no verified product-specific content exists.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="62" customHeight="1">
@@ -1936,14 +2918,14 @@
       <x:c r="E24" s="20" t="str">
         <x:v>Blue Nova / Rebekah</x:v>
       </x:c>
-      <x:c r="F24" s="20" t="str">
-        <x:v>Pending access</x:v>
+      <x:c r="F24" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="G24" s="20" t="str">
-        <x:v>Rebekah approves exact list, missing content, and final customer presentation.</x:v>
+        <x:v>The exact 25 are saved locally; all are active/online, with remaining gaps tracked in this sheet.</x:v>
       </x:c>
       <x:c r="H24" s="20" t="str">
-        <x:v>Blue Nova produces the list; client does not build a separate sheet.</x:v>
+        <x:v>Next proof is the first Kosmos pull, not another product-selection request.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1965,7 +2947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ec80e319e26476c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c02848e8ca34296"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1988,10 +2970,16 @@
         <x:v>Phase Two Decisions, Access, and Prerequisite Gate</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+    <x:row r="2" ht="56" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Confirmed items may appear in local mockups. Proposed or pending items remain provisional. No staging, integration trial, purchase, or live work begins until the applicable prerequisite gate is complete.</x:v>
-      </x:c>
+        <x:v>Updated through August 30, 2026. Mark's 25-product Revel export is saved and inspected: every product is Active and marked for online/third-party applications. Remaining content, identifier, weight, inventory, access, and live-sync checks stay open below.</x:v>
+      </x:c>
+      <x:c r="B2" s="28"/>
+      <x:c r="C2" s="28"/>
+      <x:c r="D2" s="28"/>
+      <x:c r="E2" s="28"/>
+      <x:c r="F2" s="28"/>
+      <x:c r="G2" s="28"/>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="9" t="str">
@@ -2006,14 +2994,14 @@
       </x:c>
       <x:c r="D3" s="13" t="n">
         <x:f>COUNTIF(D6:D28,"Confirmed")</x:f>
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
         <x:v>Needs approval</x:v>
       </x:c>
       <x:c r="F3" s="13" t="n">
         <x:f>COUNTIF(D6:D28,"Needs approval")</x:f>
-        <x:v>10</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
         <x:v>Current work: local only</x:v>
@@ -2142,10 +3130,10 @@
         <x:v>PO boxes</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
-        <x:v>Not yet decided</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="str">
-        <x:v>Needs approval</x:v>
+        <x:v>Do not allow PO boxes</x:v>
+      </x:c>
+      <x:c r="D10" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E10" s="20" t="str">
         <x:v>Checkout and policy</x:v>
@@ -2154,7 +3142,7 @@
         <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="G10" s="20" t="str">
-        <x:v>Approve before shipping configuration.</x:v>
+        <x:v>Add checkout validation and matching policy wording.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="61" customHeight="1">
@@ -2180,7 +3168,7 @@
         <x:v>Flag known exceptions during pilot selection.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="61" customHeight="1">
+    <x:row r="12" ht="48" hidden="0" customHeight="1">
       <x:c r="A12" s="20" t="str">
         <x:v>Accounts</x:v>
       </x:c>
@@ -2188,19 +3176,19 @@
         <x:v>Guest checkout and accounts</x:v>
       </x:c>
       <x:c r="C12" s="20" t="str">
-        <x:v>Guest checkout with optional accounts proposed</x:v>
-      </x:c>
-      <x:c r="D12" s="20" t="str">
-        <x:v>Needs approval</x:v>
+        <x:v>Guest checkout allowed; optional customer accounts use standard email/password access; no customer 2FA; staff/admin backend protection is separate</x:v>
+      </x:c>
+      <x:c r="D12" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E12" s="20" t="str">
-        <x:v>Checkout and account system</x:v>
+        <x:v>Checkout, account system, security, and training</x:v>
       </x:c>
       <x:c r="F12" s="20" t="str">
-        <x:v>Rebekah</x:v>
+        <x:v>Rebekah / Blue Nova</x:v>
       </x:c>
       <x:c r="G12" s="20" t="str">
-        <x:v>Approve before final copy/configuration.</x:v>
+        <x:v>Configure and test guest checkout, optional accounts, password reset, email delivery, consent, and privacy on staging. Configure staff/administrator backend protection separately from the customer flow.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="61" customHeight="1">
@@ -2211,10 +3199,10 @@
         <x:v>Backorders</x:v>
       </x:c>
       <x:c r="C13" s="20" t="str">
-        <x:v>Off proposed</x:v>
-      </x:c>
-      <x:c r="D13" s="20" t="str">
-        <x:v>Needs approval</x:v>
+        <x:v>Off</x:v>
+      </x:c>
+      <x:c r="D13" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E13" s="20" t="str">
         <x:v>Product/cart behavior</x:v>
@@ -2223,7 +3211,7 @@
         <x:v>Rebekah / Blue Nova</x:v>
       </x:c>
       <x:c r="G13" s="20" t="str">
-        <x:v>Validate with sync, then approve.</x:v>
+        <x:v>Configure and verify with the first synchronized order.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="61" customHeight="1">
@@ -2234,10 +3222,10 @@
         <x:v>Safety buffer</x:v>
       </x:c>
       <x:c r="C14" s="20" t="str">
-        <x:v>One unit proposed unless sync is immediate</x:v>
-      </x:c>
-      <x:c r="D14" s="20" t="str">
-        <x:v>Needs approval</x:v>
+        <x:v>Hold back one unit unless sync testing supports removal</x:v>
+      </x:c>
+      <x:c r="D14" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E14" s="20" t="str">
         <x:v>Oversell protection</x:v>
@@ -2246,7 +3234,7 @@
         <x:v>Rebekah / Blue Nova</x:v>
       </x:c>
       <x:c r="G14" s="20" t="str">
-        <x:v>Validate sync timing, then approve.</x:v>
+        <x:v>Measure sync timing during the pilot before changing the buffer.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="61" customHeight="1">
@@ -2303,10 +3291,10 @@
         <x:v>Tax rules and tax on shipping</x:v>
       </x:c>
       <x:c r="C17" s="20" t="str">
-        <x:v>Not supplied</x:v>
-      </x:c>
-      <x:c r="D17" s="20" t="str">
-        <x:v>Needs approval</x:v>
+        <x:v>Treat dietary supplements as Michigan tax-exempt food per client direction</x:v>
+      </x:c>
+      <x:c r="D17" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E17" s="20" t="str">
         <x:v>Checkout and testing</x:v>
@@ -2315,7 +3303,7 @@
         <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="G17" s="20" t="str">
-        <x:v>Provide approved configuration direction.</x:v>
+        <x:v>Verify tax and shipping totals with test orders before launch.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="61" customHeight="1">
@@ -2349,10 +3337,10 @@
         <x:v>Order/customer-service email</x:v>
       </x:c>
       <x:c r="C19" s="20" t="str">
-        <x:v>Not supplied</x:v>
-      </x:c>
-      <x:c r="D19" s="20" t="str">
-        <x:v>Needs approval</x:v>
+        <x:v>rebekahspureliving@gmail.com and clarkstonpurchaser@rebekahspureliving.com</x:v>
+      </x:c>
+      <x:c r="D19" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E19" s="20" t="str">
         <x:v>Notifications and customer help</x:v>
@@ -2361,7 +3349,7 @@
         <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="G19" s="20" t="str">
-        <x:v>Approve operational address and response details.</x:v>
+        <x:v>Configure both recipients and test every required notification.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="61" customHeight="1">
@@ -2410,7 +3398,7 @@
         <x:v>Approve after operational rules are settled.</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="61" customHeight="1">
+    <x:row r="22" ht="66" customHeight="1">
       <x:c r="A22" s="20" t="str">
         <x:v>Pilot</x:v>
       </x:c>
@@ -2418,10 +3406,10 @@
         <x:v>Twenty-five representative products</x:v>
       </x:c>
       <x:c r="C22" s="20" t="str">
-        <x:v>Not selected/prepared</x:v>
-      </x:c>
-      <x:c r="D22" s="20" t="str">
-        <x:v>Pending product data</x:v>
+        <x:v>Mark's 25-product export is saved; all 25 show Active = Yes and online/third-party = Yes</x:v>
+      </x:c>
+      <x:c r="D22" s="30" t="str">
+        <x:v>In progress</x:v>
       </x:c>
       <x:c r="E22" s="20" t="str">
         <x:v>Integration pilot</x:v>
@@ -2430,10 +3418,10 @@
         <x:v>Rebekah / Mark</x:v>
       </x:c>
       <x:c r="G22" s="20" t="str">
-        <x:v>Prepare in Revel and enable only intended items.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="61" customHeight="1">
+        <x:v>Run the first Kosmos pull to prove all 25 appear, then reconcile missing SKU, descriptions, weight, inventory, and media.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="62" customHeight="1">
       <x:c r="A23" s="20" t="str">
         <x:v>Access</x:v>
       </x:c>
@@ -2441,9 +3429,9 @@
         <x:v>Revel administrator/integration access</x:v>
       </x:c>
       <x:c r="C23" s="20" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="D23" s="20" t="str">
+        <x:v>Revel invitation received and password created; Clarkston integration permissions not verified</x:v>
+      </x:c>
+      <x:c r="D23" s="25" t="str">
         <x:v>Pending access</x:v>
       </x:c>
       <x:c r="E23" s="20" t="str">
@@ -2453,10 +3441,10 @@
         <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="G23" s="20" t="str">
-        <x:v>Provide establishment-capable access.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="61" customHeight="1">
+        <x:v>Log in and verify establishment-level product and integration permissions.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="62" customHeight="1">
       <x:c r="A24" s="20" t="str">
         <x:v>Access</x:v>
       </x:c>
@@ -2464,10 +3452,10 @@
         <x:v>Client-owned Kosmos account and configuration access</x:v>
       </x:c>
       <x:c r="C24" s="20" t="str">
-        <x:v>Not available</x:v>
-      </x:c>
-      <x:c r="D24" s="20" t="str">
-        <x:v>Pending access</x:v>
+        <x:v>Client-owned account created; 14-day trial active; access supplied</x:v>
+      </x:c>
+      <x:c r="D24" s="23" t="str">
+        <x:v>Confirmed</x:v>
       </x:c>
       <x:c r="E24" s="20" t="str">
         <x:v>Integration</x:v>
@@ -2476,20 +3464,20 @@
         <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="G24" s="20" t="str">
-        <x:v>Create only when test window is ready.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="61" customHeight="1">
+        <x:v>Blue Nova creates the WooCommerce key/secret and performs the first connection test.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="62" customHeight="1">
       <x:c r="A25" s="20" t="str">
         <x:v>Access</x:v>
       </x:c>
       <x:c r="B25" s="20" t="str">
-        <x:v>USPS account/API and live-rate extension</x:v>
+        <x:v>USPS account/API and live-rate plugin</x:v>
       </x:c>
       <x:c r="C25" s="20" t="str">
-        <x:v>Business account exists; integration access/extension not active</x:v>
-      </x:c>
-      <x:c r="D25" s="20" t="str">
+        <x:v>USPS business account exists; developer/API access and plugin setup are not confirmed</x:v>
+      </x:c>
+      <x:c r="D25" s="25" t="str">
         <x:v>Pending access</x:v>
       </x:c>
       <x:c r="E25" s="20" t="str">
@@ -2499,7 +3487,7 @@
         <x:v>Rebekah / Blue Nova</x:v>
       </x:c>
       <x:c r="G25" s="20" t="str">
-        <x:v>Purchase/connect only after approval and test readiness.</x:v>
+        <x:v>Authorize USPS API access and test the free live-rate plugin before any paid upgrade.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="61" customHeight="1">
@@ -2548,7 +3536,7 @@
         <x:v>Do not create or purchase during local design phase.</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="61" customHeight="1">
+    <x:row r="28" ht="58" customHeight="1">
       <x:c r="A28" s="20" t="str">
         <x:v>Schedule</x:v>
       </x:c>
@@ -2556,9 +3544,9 @@
         <x:v>Safe working window</x:v>
       </x:c>
       <x:c r="C28" s="20" t="str">
-        <x:v>Must avoid blackout dates/weekends and preserve recovery time</x:v>
-      </x:c>
-      <x:c r="D28" s="20" t="str">
+        <x:v>Kosmos 14-day trial is active; exact expiration date and safe test window must be confirmed</x:v>
+      </x:c>
+      <x:c r="D28" s="25" t="str">
         <x:v>Needs approval</x:v>
       </x:c>
       <x:c r="E28" s="20" t="str">
@@ -2568,7 +3556,7 @@
         <x:v>Todd / Rebekah</x:v>
       </x:c>
       <x:c r="G28" s="20" t="str">
-        <x:v>Confirm before starting any time-limited trial or active integration.</x:v>
+        <x:v>Confirm the expiration date before starting the Revel/WooCommerce connection test.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2590,7 +3578,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reee62ffff74a436c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fa967d4f564ac7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2612,10 +3600,15 @@
         <x:v>Phase Two End-to-End Implementation Plan</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="36" customHeight="1">
+    <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>The first seven rows are the current local approval workflow. Every later row is future gated work and is documented here so nothing is improvised after design approval.</x:v>
-      </x:c>
+        <x:v>All seven exact current ecommerce mockup systems are internally approved and frozen while Rebekah reviews them. Local readiness documents and the dormant WooCommerce scaffold were completed September 2, 2026; external and staging work remains gated.</x:v>
+      </x:c>
+      <x:c r="B2" s="28"/>
+      <x:c r="C2" s="28"/>
+      <x:c r="D2" s="28"/>
+      <x:c r="E2" s="28"/>
+      <x:c r="F2" s="28"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="17" t="str">
@@ -2637,7 +3630,7 @@
         <x:v>Required Gate / Output</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="72" customHeight="1">
+    <x:row r="5" ht="60" customHeight="1">
       <x:c r="A5" s="21" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -2645,19 +3638,19 @@
         <x:v>Approve global commerce add-on</x:v>
       </x:c>
       <x:c r="C5" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E5" s="20" t="str">
-        <x:v>Review literal header/footer additions against approved Phase One chrome at desktop, tablet, and phone.</x:v>
+        <x:v>Exact Header + Footer Ecommerce Add-On v1.5 is internally approved and frozen. No WordPress implementation begins before Rebekah approves this version.</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>Approved system 01</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="72" customHeight="1">
+        <x:v>Rebekah approves exact system 01 v1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="21" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -2665,19 +3658,19 @@
         <x:v>Approve Online Store homepage</x:v>
       </x:c>
       <x:c r="C6" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E6" s="20" t="str">
-        <x:v>Rebuild the recovered early store-home direction using approved chrome and controlled samples.</x:v>
+        <x:v>Exact Main Homepage Ecommerce Integration v1.9 is internally approved and frozen. Its Shop Online control routes to the separate store page.</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
-        <x:v>Approved system 02</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="72" customHeight="1">
+        <x:v>Rebekah approves exact system 02 v1.9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="60" customHeight="1">
       <x:c r="A7" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -2685,19 +3678,19 @@
         <x:v>Approve catalog template</x:v>
       </x:c>
       <x:c r="C7" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E7" s="20" t="str">
-        <x:v>Create Shop All/archive, cards, search, filters, sorting, pagination, and no-results behavior.</x:v>
+        <x:v>Exact Shop Homepage + Product Catalog v1.8 is internally approved and frozen; connected product fields remain a later one-product validation task.</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
-        <x:v>Approved system 03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="72" customHeight="1">
+        <x:v>Rebekah approves exact system 03 v1.8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="60" customHeight="1">
       <x:c r="A8" s="21" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -2705,19 +3698,19 @@
         <x:v>Approve product pages</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>Create simple and variable product examples with all required content, stock, warning, and variation states.</x:v>
+        <x:v>Exact Product Page Templates v1.7 is internally approved and frozen; connected data and verified source content remain later implementation gates.</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>Approved system 04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="72" customHeight="1">
+        <x:v>Rebekah approves exact system 04 v1.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="60" customHeight="1">
       <x:c r="A9" s="21" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -2725,19 +3718,19 @@
         <x:v>Approve purchase path</x:v>
       </x:c>
       <x:c r="C9" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E9" s="20" t="str">
-        <x:v>Create connected cart, checkout, validation, and confirmation prototype.</x:v>
+        <x:v>Exact Purchase Path v1.6 is internally approved and frozen; payment, shipping, tax, email, and order behavior remain connected-service tests.</x:v>
       </x:c>
       <x:c r="F9" s="20" t="str">
-        <x:v>Approved system 05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="72" customHeight="1">
+        <x:v>Rebekah approves exact system 05 v1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="60" hidden="0" customHeight="1">
       <x:c r="A10" s="21" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -2745,19 +3738,19 @@
         <x:v>Approve account system</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E10" s="20" t="str">
-        <x:v>Create login, optional registration, reset, dashboard, addresses, and order states.</x:v>
+        <x:v>Exact Customer Account System v1.6 is internally approved and frozen with guest checkout, optional accounts, and no customer 2FA.</x:v>
       </x:c>
       <x:c r="F10" s="20" t="str">
-        <x:v>Approved system 06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="72" customHeight="1">
+        <x:v>Rebekah approves exact system 06 v1.6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="60" customHeight="1">
       <x:c r="A11" s="21" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -2765,16 +3758,16 @@
         <x:v>Approve states + complete design QA</x:v>
       </x:c>
       <x:c r="C11" s="20" t="str">
-        <x:v>Current: local</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:v>Blue Nova / Todd / Rebekah</x:v>
       </x:c>
       <x:c r="E11" s="20" t="str">
-        <x:v>Approve edge states and cross-system responsive/accessibility behavior; record revisions and approve full set.</x:v>
+        <x:v>Exact Store States + Components v1.5 is internally approved and frozen; provider-specific error text remains implementation validation.</x:v>
       </x:c>
       <x:c r="F11" s="20" t="str">
-        <x:v>Approved system 07 + client design approval</x:v>
+        <x:v>Rebekah approves exact system 07 v1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">
@@ -2891,10 +3884,10 @@
         <x:v>Blue Nova / Rebekah</x:v>
       </x:c>
       <x:c r="E17" s="20" t="str">
-        <x:v>Pass QA/acceptance sheet, preserve new production content, obtain client approval, train staff, launch in controlled window, and monitor stabilization before full-catalog planning.</x:v>
+        <x:v>Pass QA and acceptance, obtain client approval, create and deliver the welcome packet with instructional videos, written guides, support boundaries, and escalation contacts; train designated staff; launch in a controlled window; and monitor stabilization before full-catalog planning.</x:v>
       </x:c>
       <x:c r="F17" s="20" t="str">
-        <x:v>All tests pass; client signoff; controlled launch and handoff</x:v>
+        <x:v>All tests pass; client signoff; welcome packet delivered; staff training acknowledged; controlled launch and handoff.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2904,7 +3897,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9797df4c4d354b71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02bc2a6d1c34423d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3254,7 +4247,7 @@
       </x:c>
       <x:c r="G18" s="20" t="str"/>
     </x:row>
-    <x:row r="19" ht="58" customHeight="1">
+    <x:row r="19" ht="36" hidden="0" customHeight="1">
       <x:c r="A19" s="21" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -3262,10 +4255,10 @@
         <x:v>Accounts</x:v>
       </x:c>
       <x:c r="C19" s="20" t="str">
-        <x:v>Guest/account checkout, consent, login, password reset, addresses, and order history work.</x:v>
+        <x:v>Guest checkout works without an account. Optional account creation, consent, login, password reset, addresses, and order history all work. Customer 2FA is not shown or required. Staff/administrator backend protection is tested separately.</x:v>
       </x:c>
       <x:c r="D19" s="20" t="str">
-        <x:v>Customer journey QA</x:v>
+        <x:v>Customer journey + security QA</x:v>
       </x:c>
       <x:c r="E19" s="20" t="str">
         <x:v>Blue Nova</x:v>
@@ -3273,7 +4266,9 @@
       <x:c r="F19" s="20" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="G19" s="20" t="str"/>
+      <x:c r="G19" s="20" t="str">
+        <x:v>Record guest checkout, optional-account creation, sign-in, reset-email, address, order-history, accessibility, and separate staff/admin backend-security evidence.</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" s="21" t="n">
@@ -3506,7 +4501,7 @@
       </x:c>
       <x:c r="G30" s="20" t="str"/>
     </x:row>
-    <x:row r="31" ht="58" customHeight="1">
+    <x:row r="31" ht="82" customHeight="1">
       <x:c r="A31" s="21" t="n">
         <x:v>26</x:v>
       </x:c>
@@ -3514,7 +4509,7 @@
         <x:v>Training</x:v>
       </x:c>
       <x:c r="C31" s="20" t="str">
-        <x:v>Selected staff are trained on Revel maintenance, online eligibility, fulfillment, orders, refunds, and escalation.</x:v>
+        <x:v>The welcome packet is delivered and designated staff complete the instructional videos, written guides, live walkthrough, and escalation review for accounts, orders, Revel maintenance, fulfillment, refunds, and customer support.</x:v>
       </x:c>
       <x:c r="D31" s="20" t="str">
         <x:v>Prelaunch</x:v>
@@ -3525,7 +4520,9 @@
       <x:c r="F31" s="20" t="str">
         <x:v>Not started</x:v>
       </x:c>
-      <x:c r="G31" s="20" t="str"/>
+      <x:c r="G31" s="20" t="str">
+        <x:v>Record the packet link, video links, written guides, staff attendees, acknowledgment, and escalation contact sheet.</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
       <x:c r="A32" s="21" t="n">
@@ -3588,7 +4585,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8f47403f4c34e20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd96fbfb9b2f420a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3693,7 +4690,7 @@
         <x:v>Design approval</x:v>
       </x:c>
       <x:c r="C7" s="20" t="str">
-        <x:v>Seven reusable responsive systems</x:v>
+        <x:v>Seven reusable responsive systems internally approved; Rebekah client approval pending</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>Blue Nova / Todd / Rebekah</x:v>
@@ -3702,33 +4699,33 @@
         <x:v>Current local phase</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
-        <x:v>In progress</x:v>
+        <x:v>Awaiting client approval</x:v>
       </x:c>
       <x:c r="G7" s="20" t="str">
         <x:v>No WordPress or hosting work.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="62" customHeight="1">
+    <x:row r="8" ht="72" hidden="0" customHeight="1">
       <x:c r="A8" s="20" t="str">
         <x:v>Software</x:v>
       </x:c>
       <x:c r="B8" s="20" t="str">
-        <x:v>WooCommerce core</x:v>
+        <x:v>WooCommerce core customer accounts</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>$0; retained but inactive until protected staging is ready</x:v>
+        <x:v>$0 additional customer-account software planned; guest checkout and standard My Account features are included with WooCommerce core</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
-        <x:v>Existing project</x:v>
+        <x:v>Existing project / Rebekah</x:v>
       </x:c>
       <x:c r="E8" s="20" t="str">
-        <x:v>Future staging</x:v>
-      </x:c>
-      <x:c r="F8" s="20" t="str">
-        <x:v>No purchase required</x:v>
+        <x:v>Before protected staging</x:v>
+      </x:c>
+      <x:c r="F8" s="87" t="str">
+        <x:v>Included</x:v>
       </x:c>
       <x:c r="G8" s="20" t="str">
-        <x:v>Current project record.</x:v>
+        <x:v>No customer 2FA extension or customer-verification purchase is planned. Staff/administrator backend protection is a separate staging security task; confirm the approved compatible method and any cost before launch.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
@@ -3739,16 +4736,16 @@
         <x:v>Kosmos eSync Warmup</x:v>
       </x:c>
       <x:c r="C9" s="20" t="str">
-        <x:v>$49 month-to-month or $39/month billed annually; advertised trial</x:v>
+        <x:v>$49 month-to-month or $39/month billed annually; 14-day trial is currently active</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="E9" s="20" t="str">
-        <x:v>Ready test window</x:v>
-      </x:c>
-      <x:c r="F9" s="20" t="str">
-        <x:v>Future approval</x:v>
+        <x:v>Active trial window</x:v>
+      </x:c>
+      <x:c r="F9" s="27" t="str">
+        <x:v>Active trial</x:v>
       </x:c>
       <x:c r="G9" s="20" t="str">
         <x:v>Reverify: https://kosmoscentral.com/esync-cloud-pricing-monthly</x:v>
@@ -3759,10 +4756,10 @@
         <x:v>Software</x:v>
       </x:c>
       <x:c r="B10" s="20" t="str">
-        <x:v>Official USPS live-rate extension</x:v>
+        <x:v>USPS live-rate plugin (free pilot first)</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
-        <x:v>$109/year recorded assumption</x:v>
+        <x:v>Test the free Octolize USPS live-rate plugin; use paid PRO only if testing proves advanced packing is required</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
         <x:v>Rebekah</x:v>
@@ -3770,11 +4767,11 @@
       <x:c r="E10" s="20" t="str">
         <x:v>Shipping configuration</x:v>
       </x:c>
-      <x:c r="F10" s="20" t="str">
-        <x:v>Future approval</x:v>
+      <x:c r="F10" s="25" t="str">
+        <x:v>No purchase yet</x:v>
       </x:c>
       <x:c r="G10" s="20" t="str">
-        <x:v>Reverify: https://woocommerce.com/products/usps-shipping-method/</x:v>
+        <x:v>Reverify before purchase: https://octolize.com/product/usps-woocommerce-live-rates-pro-plugin/</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
@@ -4044,7 +5041,847 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re52d6b50055c43ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f189943e9a4e35"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="6" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="36" customHeight="1">
+      <x:c r="A1" s="36" t="str">
+        <x:v>Rebekah's Phase Two Ecommerce Mockup Version Register</x:v>
+      </x:c>
+      <x:c r="B1" s="36"/>
+      <x:c r="C1" s="36"/>
+      <x:c r="D1" s="36"/>
+      <x:c r="E1" s="36"/>
+      <x:c r="F1" s="36"/>
+      <x:c r="G1" s="36"/>
+      <x:c r="H1" s="36"/>
+      <x:c r="I1" s="36"/>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="40" t="str">
+        <x:v>Permanent rule: each mockup starts at v1.1; each reviewed revision advances to v1.2, v1.3, and so on; earlier reviewed files remain preserved; internal and client approval are separate gates tied to an exact version.</x:v>
+      </x:c>
+      <x:c r="B2" s="40"/>
+      <x:c r="C2" s="40"/>
+      <x:c r="D2" s="40"/>
+      <x:c r="E2" s="40"/>
+      <x:c r="F2" s="40"/>
+      <x:c r="G2" s="40"/>
+      <x:c r="H2" s="40"/>
+      <x:c r="I2" s="40"/>
+    </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="41" t="str">
+        <x:v>Systems</x:v>
+      </x:c>
+      <x:c r="B3" s="44" t="n">
+        <x:f>COUNTA(B6:B12)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C3" s="41" t="str">
+        <x:v>Versioned</x:v>
+      </x:c>
+      <x:c r="D3" s="44" t="n">
+        <x:f>COUNTIF(C6:C12,"&lt;&gt;Not started")</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="41" t="str">
+        <x:v>Awaiting client</x:v>
+      </x:c>
+      <x:c r="F3" s="44" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G3" s="41" t="str">
+        <x:v>Client approved</x:v>
+      </x:c>
+      <x:c r="H3" s="44" t="n">
+        <x:f>COUNTIF(E6:E12,"Client Approved")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" s="45" t="str">
+        <x:v>Gates: Client approval</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="54" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B5" s="54" t="str">
+        <x:v>Mockup System</x:v>
+      </x:c>
+      <x:c r="C5" s="54" t="str">
+        <x:v>Current Version</x:v>
+      </x:c>
+      <x:c r="D5" s="54" t="str">
+        <x:v>Latest File</x:v>
+      </x:c>
+      <x:c r="E5" s="54" t="str">
+        <x:v>Revision Status</x:v>
+      </x:c>
+      <x:c r="F5" s="54" t="str">
+        <x:v>Internal Approval</x:v>
+      </x:c>
+      <x:c r="G5" s="54" t="str">
+        <x:v>Client Approval</x:v>
+      </x:c>
+      <x:c r="H5" s="54" t="str">
+        <x:v>Next Version</x:v>
+      </x:c>
+      <x:c r="I5" s="54" t="str">
+        <x:v>Tracking Note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
+      <x:c r="A6" s="57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="55" t="str">
+        <x:v>Header + Footer Ecommerce Add-On</x:v>
+      </x:c>
+      <x:c r="C6" s="57" t="str">
+        <x:v>v1.5</x:v>
+      </x:c>
+      <x:c r="D6" s="55" t="str">
+        <x:v>online-store-header-footer-add-on-v1.5.html</x:v>
+      </x:c>
+      <x:c r="E6" s="55" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F6" s="55" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G6" s="55" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H6" s="57" t="str">
+        <x:v>v1.6</x:v>
+      </x:c>
+      <x:c r="I6" s="55" t="str">
+        <x:v>Exact v1.5 internally approved September 2, 2026. The local header, tablet, and footer Online Store links open Shop Homepage + Product Catalog v1.8; production will use /shop/. v1.4 remains preserved as superseded history. Any later design change requires v1.6 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
+      <x:c r="A7" s="58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="56" t="str">
+        <x:v>Main Homepage Ecommerce Integration</x:v>
+      </x:c>
+      <x:c r="C7" s="58" t="str">
+        <x:v>v1.9</x:v>
+      </x:c>
+      <x:c r="D7" s="56" t="str">
+        <x:v>main-homepage-ecommerce-integration-v1.9.html</x:v>
+      </x:c>
+      <x:c r="E7" s="56" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F7" s="56" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G7" s="56" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H7" s="58" t="str">
+        <x:v>v1.10</x:v>
+      </x:c>
+      <x:c r="I7" s="56" t="str">
+        <x:v>Exact v1.9 internally approved September 2, 2026. The Shop Online hero entry opens the separate Shop Homepage + Product Catalog v1.8 preview; production will use /shop/. It preserves the v1.8 numbering removal, approved imagery, copy, components, all other interactions, review-only addition labels, and page-body-only architecture. v1.8 is superseded without approval. Any later design change requires v1.10 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
+      <x:c r="A8" s="57" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="55" t="str">
+        <x:v>Shop Homepage + Product Catalog</x:v>
+      </x:c>
+      <x:c r="C8" s="57" t="str">
+        <x:v>v1.8</x:v>
+      </x:c>
+      <x:c r="D8" s="55" t="str">
+        <x:v>shop-catalog-template-v1.8.html</x:v>
+      </x:c>
+      <x:c r="E8" s="55" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F8" s="55" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G8" s="55" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H8" s="57" t="str">
+        <x:v>v1.9</x:v>
+      </x:c>
+      <x:c r="I8" s="55" t="str">
+        <x:v>Exact v1.8 internally approved August 31, 2026. Approval covers the complete catalog design and interactions shown in the mockup. Revel/Kosmos product data, sync, inventory, pricing, category mapping, real photography, and final content remain separate implementation-validation gates. Any later design change requires v1.9 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A9" s="58" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="56" t="str">
+        <x:v>Product Page Templates</x:v>
+      </x:c>
+      <x:c r="C9" s="58" t="str">
+        <x:v>v1.7</x:v>
+      </x:c>
+      <x:c r="D9" s="56" t="str">
+        <x:v>product-page-templates-v1.7.html</x:v>
+      </x:c>
+      <x:c r="E9" s="56" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F9" s="56" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G9" s="56" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H9" s="58" t="str">
+        <x:v>v1.8</x:v>
+      </x:c>
+      <x:c r="I9" s="56" t="str">
+        <x:v>Exact v1.7 internally approved August 31, 2026. Approval covers the complete product-page design and interactions shown in the mockup. Revel/Kosmos product data, real photography, and verified manufacturer, supplier, label, or approved-catalog Directions &amp; Warnings remain separate implementation-validation gates. Any later design change requires v1.8 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="58" customHeight="1">
+      <x:c r="A10" s="57" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="55" t="str">
+        <x:v>Purchase Path</x:v>
+      </x:c>
+      <x:c r="C10" s="57" t="str">
+        <x:v>v1.6</x:v>
+      </x:c>
+      <x:c r="D10" s="55" t="str">
+        <x:v>purchase-path-mockup-v1.6.html</x:v>
+      </x:c>
+      <x:c r="E10" s="55" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F10" s="55" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G10" s="55" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H10" s="57" t="str">
+        <x:v>v1.7</x:v>
+      </x:c>
+      <x:c r="I10" s="55" t="str">
+        <x:v>Exact v1.6 internally approved August 31, 2026. Approval covers the complete cart-to-confirmation design and interactions shown in the mockup. Payment, shipping, tax, email, inventory, order, provider-message, and Revel/Kosmos behavior remain separate connected-service implementation-validation gates. Any later design change requires v1.7 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A11" s="88" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" s="89" t="str">
+        <x:v>Customer Account System</x:v>
+      </x:c>
+      <x:c r="C11" s="88" t="str">
+        <x:v>v1.6</x:v>
+      </x:c>
+      <x:c r="D11" s="89" t="str">
+        <x:v>customer-account-system-v1.6.html</x:v>
+      </x:c>
+      <x:c r="E11" s="89" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F11" s="89" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G11" s="89" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H11" s="88" t="str">
+        <x:v>v1.7</x:v>
+      </x:c>
+      <x:c r="I11" s="89" t="str">
+        <x:v>Exact v1.6 internally approved September 1, 2026. Approval covers guest checkout, automatic optional customer accounts, standard sign-in and recovery, dashboard, addresses, orders, order detail, representative interactions, and no customer 2FA. Staff/administrator backend security and all connected-service behavior remain separate staging and implementation-validation gates. Any later design change requires v1.7 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12" s="57" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="55" t="str">
+        <x:v>Store States + Components</x:v>
+      </x:c>
+      <x:c r="C12" s="57" t="str">
+        <x:v>v1.5</x:v>
+      </x:c>
+      <x:c r="D12" s="55" t="str">
+        <x:v>store-states-components-v1.5.html</x:v>
+      </x:c>
+      <x:c r="E12" s="55" t="str">
+        <x:v>Awaiting Client Approval</x:v>
+      </x:c>
+      <x:c r="F12" s="55" t="str">
+        <x:v>Approved by Todd</x:v>
+      </x:c>
+      <x:c r="G12" s="55" t="str">
+        <x:v>Pending Rebekah</x:v>
+      </x:c>
+      <x:c r="H12" s="57" t="str">
+        <x:v>v1.6</x:v>
+      </x:c>
+      <x:c r="I12" s="55" t="str">
+        <x:v>Exact v1.5 internally approved September 1, 2026. Approval covers no-results, empty-filter, out-of-stock, unavailable-variation, approved missing-photo, loading, empty-cart, checkout-validation, payment-failure, mobile-filter, and responsive/accessibility states. Connected-service wording remains an implementation-validation gate. Any later design change requires v1.6 and a new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="26" customHeight="1">
+      <x:c r="A14" s="35" t="str">
+        <x:v>Required update sequence for every revision</x:v>
+      </x:c>
+      <x:c r="B14" s="35"/>
+      <x:c r="C14" s="35"/>
+      <x:c r="D14" s="35"/>
+      <x:c r="E14" s="35"/>
+      <x:c r="F14" s="35"/>
+      <x:c r="G14" s="35"/>
+      <x:c r="H14" s="35"/>
+      <x:c r="I14" s="35"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="61" t="str">
+        <x:v>1. Save the new revision as the next versioned file; never overwrite the prior reviewed file.
+2. Update this Version Register and PHASE-TWO-MOCKUP-VERSION-REGISTER.md.
+3. Update the local review hub so it links only to the newest reviewable version.
+4. Record internal approval, client approval, or superseded status for the exact version in CLIENT-NOTES.md.</x:v>
+      </x:c>
+      <x:c r="B15" s="61"/>
+      <x:c r="C15" s="61"/>
+      <x:c r="D15" s="61"/>
+      <x:c r="E15" s="61"/>
+      <x:c r="F15" s="61"/>
+      <x:c r="G15" s="61"/>
+      <x:c r="H15" s="61"/>
+      <x:c r="I15" s="61"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="61"/>
+      <x:c r="B16" s="61"/>
+      <x:c r="C16" s="61"/>
+      <x:c r="D16" s="61"/>
+      <x:c r="E16" s="61"/>
+      <x:c r="F16" s="61"/>
+      <x:c r="G16" s="61"/>
+      <x:c r="H16" s="61"/>
+      <x:c r="I16" s="61"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="61"/>
+      <x:c r="B17" s="61"/>
+      <x:c r="C17" s="61"/>
+      <x:c r="D17" s="61"/>
+      <x:c r="E17" s="61"/>
+      <x:c r="F17" s="61"/>
+      <x:c r="G17" s="61"/>
+      <x:c r="H17" s="61"/>
+      <x:c r="I17" s="61"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="61"/>
+      <x:c r="B18" s="61"/>
+      <x:c r="C18" s="61"/>
+      <x:c r="D18" s="61"/>
+      <x:c r="E18" s="61"/>
+      <x:c r="F18" s="61"/>
+      <x:c r="G18" s="61"/>
+      <x:c r="H18" s="61"/>
+      <x:c r="I18" s="61"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
+    <x:mergeCell ref="A14:I14"/>
+    <x:mergeCell ref="A15:I18"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="E6:E30">
+    <x:cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="Awaiting Client Approval"/>
+    <x:cfRule type="containsText" dxfId="26" priority="2" operator="containsText" text="Client Approved"/>
+    <x:cfRule type="containsText" dxfId="27" priority="3" operator="containsText" text="Revision Needed"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="E6:E30">
+      <x:formula1>"Draft,Internal Review,Revision Needed,Internally Approved,Awaiting Client Approval,Client Approved,Superseded,Planned"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="43" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="40" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="43" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="64" t="str">
+        <x:v>Phase Two Staff Training, Welcome Packet, and Handoff Tracker</x:v>
+      </x:c>
+      <x:c r="B1" s="64"/>
+      <x:c r="C1" s="64"/>
+      <x:c r="D1" s="64"/>
+      <x:c r="E1" s="64"/>
+      <x:c r="F1" s="64"/>
+      <x:c r="G1" s="64"/>
+      <x:c r="H1" s="64"/>
+    </x:row>
+    <x:row r="2" ht="52" customHeight="1">
+      <x:c r="A2" s="68" t="str">
+        <x:v>Blue Nova prepares the materials and training. Rebekah designates the staff who will use them, confirms store procedures, attends the walkthrough, and keeps the completed packet. Staff follow documented steps and escalate technical issues; they do not diagnose the website, approve accounts, handle customer passwords, or create guest accounts.</x:v>
+      </x:c>
+      <x:c r="B2" s="68"/>
+      <x:c r="C2" s="68"/>
+      <x:c r="D2" s="68"/>
+      <x:c r="E2" s="68"/>
+      <x:c r="F2" s="68"/>
+      <x:c r="G2" s="68"/>
+      <x:c r="H2" s="68"/>
+    </x:row>
+    <x:row r="3" ht="26" customHeight="1">
+      <x:c r="A3" s="70" t="str">
+        <x:v>Items</x:v>
+      </x:c>
+      <x:c r="B3" s="74" t="n">
+        <x:f>COUNTA(B6:B18)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C3" s="70" t="str">
+        <x:v>Complete</x:v>
+      </x:c>
+      <x:c r="D3" s="74" t="n">
+        <x:f>COUNTIF(G6:G18,"Complete")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="70" t="str">
+        <x:v>Open</x:v>
+      </x:c>
+      <x:c r="F3" s="74" t="n">
+        <x:f>COUNTIF(G6:G18,"Not started")+COUNTIF(G6:G18,"In progress")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G3" s="76" t="str">
+        <x:v>Required before controlled launch</x:v>
+      </x:c>
+      <x:c r="H3" s="76"/>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="80" t="str">
+        <x:v>#</x:v>
+      </x:c>
+      <x:c r="B5" s="80" t="str">
+        <x:v>Welcome Packet Item</x:v>
+      </x:c>
+      <x:c r="C5" s="80" t="str">
+        <x:v>What Staff Will Learn or Do</x:v>
+      </x:c>
+      <x:c r="D5" s="80" t="str">
+        <x:v>Blue Nova Provides</x:v>
+      </x:c>
+      <x:c r="E5" s="80" t="str">
+        <x:v>Client Provides or Does</x:v>
+      </x:c>
+      <x:c r="F5" s="80" t="str">
+        <x:v>Timing / Gate</x:v>
+      </x:c>
+      <x:c r="G5" s="80" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H5" s="80" t="str">
+        <x:v>Evidence / Link</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="78" customHeight="1">
+      <x:c r="A6" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>Designated ecommerce support contacts</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>Know which staff members own routine account and order questions.</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>Define the support role and escalation route.</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="str">
+        <x:v>Name one primary and one backup staff contact.</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="str">
+        <x:v>Before packet production</x:v>
+      </x:c>
+      <x:c r="G6" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="str">
+        <x:v>Names and preferred contact details</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="36" hidden="0" customHeight="1">
+      <x:c r="A7" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>Access and privacy boundaries</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>Never request or view a customer password. Keep staff/administrator passwords and backend verification codes private; use approved account, order, reset, and escalation procedures only.</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>Written access, privacy, backend-security, and escalation rules.</x:v>
+      </x:c>
+      <x:c r="E7" s="20" t="str">
+        <x:v>Confirm which staff members receive WordPress, WooCommerce, Revel, or support access.</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="str">
+        <x:v>Before access is granted</x:v>
+      </x:c>
+      <x:c r="G7" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H7" s="20" t="str">
+        <x:v>Approved access list</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
+      <x:c r="A8" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>Guest checkout and optional accounts video</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>Explain that guest checkout creates no account, optional accounts are automatic, and customers use the standard email, password, and reset flow without customer 2FA.</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>Short screen-recorded walkthrough plus written account setup, sign-in, and recovery summary.</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="str">
+        <x:v>Review the customer-facing process and confirm it matches store policy.</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="str">
+        <x:v>Before customer training</x:v>
+      </x:c>
+      <x:c r="G8" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H8" s="20" t="str">
+        <x:v>Video, written guide, and tested reset path</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" hidden="0" customHeight="1">
+      <x:c r="A9" s="21" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>Password reset assistance</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>Direct customers to the standard reset flow, confirm the generic success message, and escalate missing reset emails, repeated failures, or lockouts.</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>Video, quick-reference password-reset steps, and a customer-safe response script.</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="str">
+        <x:v>Confirm the public support phone/email route staff will use.</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="str">
+        <x:v>Before launch</x:v>
+      </x:c>
+      <x:c r="G9" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H9" s="20" t="str">
+        <x:v>Video, script, and test result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" hidden="0" customHeight="1">
+      <x:c r="A10" s="21" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>Sign-in troubleshooting</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="str">
+        <x:v>Check only customer-safe basics such as the correct email, reset-link timing, and browser steps. Never handle a customer's password.</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>One-page sign-in, reset, lockout, and escalation guide.</x:v>
+      </x:c>
+      <x:c r="E10" s="20" t="str">
+        <x:v>Use the guide; escalate repeated failures, lockouts, missing reset emails, or suspected security issues.</x:v>
+      </x:c>
+      <x:c r="F10" s="20" t="str">
+        <x:v>Before launch</x:v>
+      </x:c>
+      <x:c r="G10" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H10" s="20" t="str">
+        <x:v>Guide link</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="78" customHeight="1">
+      <x:c r="A11" s="21" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>Order lookup and status questions</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="str">
+        <x:v>Locate an order, explain the visible status, and share approved next steps.</x:v>
+      </x:c>
+      <x:c r="D11" s="20" t="str">
+        <x:v>Video and written order-support procedure.</x:v>
+      </x:c>
+      <x:c r="E11" s="20" t="str">
+        <x:v>Confirm who may view orders and which statuses staff may explain or change.</x:v>
+      </x:c>
+      <x:c r="F11" s="20" t="str">
+        <x:v>Before launch</x:v>
+      </x:c>
+      <x:c r="G11" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="str">
+        <x:v>Video, procedure, and access test</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="78" customHeight="1">
+      <x:c r="A12" s="21" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="20" t="str">
+        <x:v>Changes, cancellations, refunds, and exceptions</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="str">
+        <x:v>Follow the approved decision path rather than promising an outcome.</x:v>
+      </x:c>
+      <x:c r="D12" s="20" t="str">
+        <x:v>Escalation chart and approved response templates.</x:v>
+      </x:c>
+      <x:c r="E12" s="20" t="str">
+        <x:v>Approve store rules, authorized roles, and financial limits.</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="str">
+        <x:v>After policies are approved</x:v>
+      </x:c>
+      <x:c r="G12" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H12" s="20" t="str">
+        <x:v>Policy and escalation links</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="78" customHeight="1">
+      <x:c r="A13" s="21" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>Revel product maintenance and online eligibility</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>Maintain approved names, prices, SKUs, weights, stock, and online-eligibility settings without breaking synchronization.</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="str">
+        <x:v>Video, field-ownership guide, and do-not-change list based on integration testing.</x:v>
+      </x:c>
+      <x:c r="E13" s="20" t="str">
+        <x:v>Designate the staff member who maintains Revel product data.</x:v>
+      </x:c>
+      <x:c r="F13" s="20" t="str">
+        <x:v>After one-product proof</x:v>
+      </x:c>
+      <x:c r="G13" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H13" s="20" t="str">
+        <x:v>Video, field guide, and staff name</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="78" customHeight="1">
+      <x:c r="A14" s="21" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="20" t="str">
+        <x:v>Fulfillment, packing, and shipping</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="str">
+        <x:v>Process online orders using approved packing, label, status, and exception steps.</x:v>
+      </x:c>
+      <x:c r="D14" s="20" t="str">
+        <x:v>Recorded workflow and written daily procedure.</x:v>
+      </x:c>
+      <x:c r="E14" s="20" t="str">
+        <x:v>Confirm packing staff, supplies, cutoffs, and exception handling.</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="str">
+        <x:v>After shipping configuration</x:v>
+      </x:c>
+      <x:c r="G14" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H14" s="20" t="str">
+        <x:v>Workflow, test order, and procedure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="78" customHeight="1">
+      <x:c r="A15" s="21" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>Daily operations checklist</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="str">
+        <x:v>Review new orders, exceptions, failed payments, low stock, and unresolved support items.</x:v>
+      </x:c>
+      <x:c r="D15" s="20" t="str">
+        <x:v>Printable and digital checklist.</x:v>
+      </x:c>
+      <x:c r="E15" s="20" t="str">
+        <x:v>Confirm who performs each check and the expected schedule.</x:v>
+      </x:c>
+      <x:c r="F15" s="20" t="str">
+        <x:v>Before launch</x:v>
+      </x:c>
+      <x:c r="G15" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H15" s="20" t="str">
+        <x:v>Completed checklist template</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="78" customHeight="1">
+      <x:c r="A16" s="21" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="20" t="str">
+        <x:v>Escalation matrix and support contacts</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>Know what staff handles, what Blue Nova handles, and what must go to Revel, Kosmos, shipping, or payment support.</x:v>
+      </x:c>
+      <x:c r="D16" s="20" t="str">
+        <x:v>One-page escalation matrix with contact paths and required evidence.</x:v>
+      </x:c>
+      <x:c r="E16" s="20" t="str">
+        <x:v>Approve internal contacts and keep vendor account details current in an approved secure location.</x:v>
+      </x:c>
+      <x:c r="F16" s="20" t="str">
+        <x:v>Before launch</x:v>
+      </x:c>
+      <x:c r="G16" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H16" s="20" t="str">
+        <x:v>Escalation matrix link</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="78" customHeight="1">
+      <x:c r="A17" s="21" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="str">
+        <x:v>Live staff walkthrough and questions</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>Practice the account, order, fulfillment, refund, and escalation workflows using test cases.</x:v>
+      </x:c>
+      <x:c r="D17" s="20" t="str">
+        <x:v>Focused training session, test scenarios, and Q&amp;A notes.</x:v>
+      </x:c>
+      <x:c r="E17" s="20" t="str">
+        <x:v>Ensure designated staff attend and identify any missing instructions.</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="str">
+        <x:v>Prelaunch training gate</x:v>
+      </x:c>
+      <x:c r="G17" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H17" s="20" t="str">
+        <x:v>Attendee list and open-question log</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="78" customHeight="1">
+      <x:c r="A18" s="21" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="20" t="str">
+        <x:v>Welcome packet delivery and acknowledgment</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>Know where the final videos, written instructions, checklists, and support contacts are stored.</x:v>
+      </x:c>
+      <x:c r="D18" s="20" t="str">
+        <x:v>Deliver the organized welcome packet and final handoff index.</x:v>
+      </x:c>
+      <x:c r="E18" s="20" t="str">
+        <x:v>Confirm receipt, access, designated staff, and acceptance of the handoff materials.</x:v>
+      </x:c>
+      <x:c r="F18" s="20" t="str">
+        <x:v>Required before controlled launch</x:v>
+      </x:c>
+      <x:c r="G18" s="20" t="str">
+        <x:v>Not started</x:v>
+      </x:c>
+      <x:c r="H18" s="20" t="str">
+        <x:v>Packet link and client acknowledgment</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="G3:H3"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="G6:G30">
+    <x:cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="Complete"/>
+    <x:cfRule type="containsText" dxfId="29" priority="2" operator="containsText" text="In progress"/>
+    <x:cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="Not started"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="G6:G30">
+      <x:formula1>"Not started,In progress,Complete,Not applicable"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0643dc1ae5b843bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/01a034a3-641b-70f2-bc46-4a4f5cf27673/Rebekahs-Phase-Two-Ecommerce-Workbook.xlsx
+++ b/outputs/01a034a3-641b-70f2-bc46-4a4f5cf27673/Rebekahs-Phase-Two-Ecommerce-Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Set" sheetId="1" r:id="R42148c01ad554e74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Templates &amp; Global" sheetId="2" r:id="R8c2b5b02b0a241da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product &amp; Content" sheetId="3" r:id="R46c9e4a79eb24de6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions &amp; Access" sheetId="4" r:id="R790ca0f09bcb4ec8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Plan" sheetId="5" r:id="R68303009b960456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA &amp; Launch Gates" sheetId="6" r:id="Rfbd853e192e5453a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Costs" sheetId="7" r:id="R6e5c4df8829b4571"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Register" sheetId="8" r:id="Rbef768cf8ed14612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training &amp; Handoff" sheetId="9" r:id="R12a935fa2696487c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Staging Packet" sheetId="10" r:id="R5c6213b83cdd4385"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Approval Set" sheetId="1" r:id="R1ee12911ebfa4d11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Templates &amp; Global" sheetId="2" r:id="Rbc69bd3e723a4855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product &amp; Content" sheetId="3" r:id="R0099dab77c084788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions &amp; Access" sheetId="4" r:id="R3ea2f25f85924f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Plan" sheetId="5" r:id="R9de4837aad614e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA &amp; Launch Gates" sheetId="6" r:id="R6399fccfc8ad46ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scope &amp; Costs" sheetId="7" r:id="Rdd745b9147f34cef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Register" sheetId="8" r:id="R123dd4a8a877436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Training &amp; Handoff" sheetId="9" r:id="R720d6723e4d643dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Staging Packet" sheetId="10" r:id="R222fc8f76ee14828"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -22,7 +22,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="20">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -137,8 +137,20 @@
       <x:color rgb="FF23463A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF6B501C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B501C"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="26">
+  <x:fills count="32">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -265,6 +277,36 @@
         <x:fgColor rgb="FFC5E9F6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EFD9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6E8B1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EFD9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6E8B1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EFD9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EFD9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="7">
     <x:border/>
@@ -308,7 +350,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="121">
+  <x:cellXfs count="146">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -579,6 +621,81 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="19" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="27" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="29" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="29" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="30" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="31" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -926,7 +1043,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -937,7 +1054,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -948,7 +1065,7 @@
         <x:color rgb="FF991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -959,7 +1076,7 @@
         <x:color rgb="FF3730A3"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE0E7FF"/>
         </x:patternFill>
       </x:fill>
@@ -1322,24 +1439,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>Planned</x:v>
+        <x:v>Awaiting client</x:v>
       </x:c>
       <x:c r="F3" s="13" t="n">
-        <x:f>COUNTIF(E6:E12,"Planned")+COUNTIF(E6:E12,"Planned next")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
         <x:v>Client approved</x:v>
       </x:c>
       <x:c r="H3" s="13" t="n">
-        <x:f>COUNTIF(E6:E12,"Client Approved")</x:f>
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I3" s="9" t="str">
-        <x:v>Current gates</x:v>
+        <x:v>Current gate</x:v>
       </x:c>
       <x:c r="J3" s="13" t="str">
-        <x:v>Client approval</x:v>
+        <x:v>Authorize infrastructure</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
@@ -1387,8 +1502,8 @@
       <x:c r="D6" s="20" t="str">
         <x:v>Sitewide</x:v>
       </x:c>
-      <x:c r="E6" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E6" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
         <x:v>Local mockup</x:v>
@@ -1403,7 +1518,7 @@
         <x:v>Store entry, internal links, policy links, responsive navigation, account/cart indexation.</x:v>
       </x:c>
       <x:c r="J6" s="20" t="str">
-        <x:v>Exact Header + Footer Ecommerce Add-On v1.5 was approved by Todd on September 2, 2026 and is ready for Rebekah's separate client review. In the local review, the header, tablet, and footer Online Store links open Shop Homepage + Product Catalog v1.8; production will use the real /shop/ route. v1.4 remains preserved as superseded history.</x:v>
+        <x:v>Exact Header + Footer Ecommerce Add-On v1.5 was approved by Todd and approved by Rebekah on September 2, 2026. Production Online Store links will use /shop/. Any later design change requires v1.6 and new exact-version approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="80" customHeight="1">
@@ -1419,8 +1534,8 @@
       <x:c r="D7" s="20" t="str">
         <x:v>/</x:v>
       </x:c>
-      <x:c r="E7" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E7" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
         <x:v>Local page-body mockup</x:v>
@@ -1435,10 +1550,10 @@
         <x:v>Existing homepage SEO/content remains primary; add clear internal links to /shop/ and useful product discovery without internal mockup or integration language.</x:v>
       </x:c>
       <x:c r="J7" s="20" t="str">
-        <x:v>Exact Main Homepage Ecommerce Integration v1.9 was approved by Todd on September 2, 2026 and is ready for Rebekah's separate client review. The Shop Online hero entry opens the separate Shop Homepage + Product Catalog v1.8 preview instead of jumping to the homepage ecommerce section. Production will use /shop/. v1.8 is superseded without approval; any later design change requires v1.10 and a new approval.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="80" customHeight="1">
+        <x:v>Exact Main Homepage Ecommerce Integration v1.9 was approved by Todd and approved by Rebekah on September 2, 2026. Its Shop Online control routes directly to the separate Shop page, satisfying the requirement repeated in Rebekah's email.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="130" customHeight="1">
       <x:c r="A8" s="21" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1446,13 +1561,13 @@
         <x:v>Shop Homepage + Product Catalog</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>Store introduction, four approved illustrated wellness-goal paths, personal shopping guidance, catalog search, sort, filters, six sample products, pagination, no-results recovery, and the approved sitewide missing-product-photo component</x:v>
+        <x:v>Store introduction, four illustrated wellness-goal paths, personal guidance, catalog search, sorting, six sample products, pagination, no-results recovery, the approved missing-photo component, and two expandable filter groups for Brands and Wellness Categories</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>/shop/ and shared archives</x:v>
       </x:c>
-      <x:c r="E8" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E8" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
         <x:v>Local page-body mockup</x:v>
@@ -1461,13 +1576,13 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H8" s="20" t="str">
-        <x:v>Use /shop/ as both the store homepage and full catalog. Keep the customer-facing toolbar personal and helpful instead of emphasizing sample-product counts. Real product data still requires Revel/Kosmos validation.</x:v>
+        <x:v>Use /shop/ as the store homepage and full catalog. The client-requested v1.9 filter revision uses exactly two compact expandable groups on desktop and mobile. Actual choices enabled for the 25-product pilot and each product's mapping remain connected-data validation.</x:v>
       </x:c>
       <x:c r="I8" s="20" t="str">
         <x:v>Unique shop introduction, category discovery, archive headings, breadcrumbs, canonicals, pagination, filter/indexation rules, card semantics, accessible result feedback, and product-help content.</x:v>
       </x:c>
       <x:c r="J8" s="20" t="str">
-        <x:v>Exact Shop Homepage + Product Catalog v1.8 was approved by Todd on August 31, 2026 and is ready for Rebekah's separate client review. This visual approval includes the page structure, wellness paths, personal messaging, benefits/help row, product cards, search, sorting, filters, load-more, no-results recovery, and sitewide missing-photo component. Revel/Kosmos data, synchronization, inventory, pricing, categories, real photography, and final product content remain separate implementation-validation gates.</x:v>
+        <x:v>Exact Shop/Catalog v1.9 approved by Todd and Rebekah on September 3, 2026. Her reply to the exact-version request says Looks great, thank you. No further changes requested. Actual product mappings remain connected-data validation. Source: https://mail.google.com/mail/#all/1a069170a83b3a6e</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="84" hidden="0" customHeight="1">
@@ -1483,8 +1598,8 @@
       <x:c r="D9" s="20" t="str">
         <x:v>/product/{slug}/</x:v>
       </x:c>
-      <x:c r="E9" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E9" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F9" s="20" t="str">
         <x:v>Local page-body mockup</x:v>
@@ -1499,7 +1614,7 @@
         <x:v>Product schema, unique copy, gallery semantics and alt text, compact product details, source-verified directions/warnings when applicable, stock language, variation errors, related items, and accessible support information.</x:v>
       </x:c>
       <x:c r="J9" s="20" t="str">
-        <x:v>Exact Product Page Templates v1.7 was approved by Todd on August 31, 2026 and is ready for Rebekah's separate client review. Approval covers both product examples, galleries, the approved missing-photo treatment, quantity and variation controls, compact details, optional source-verified Directions &amp; Warnings, phone guidance near Add to Cart, and related products. Revel/Kosmos data and verified manufacturer, supplier, label, or approved-catalog content remain separate implementation-validation gates.</x:v>
+        <x:v>Exact Product Page Templates v1.7 was approved by Todd and approved by Rebekah on September 2, 2026. Connected product data, real photography, and verified source content remain separate implementation-validation gates.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="80" customHeight="1">
@@ -1515,8 +1630,8 @@
       <x:c r="D10" s="20" t="str">
         <x:v>/cart/; /checkout/; confirmation</x:v>
       </x:c>
-      <x:c r="E10" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E10" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F10" s="20" t="str">
         <x:v>Local page-body mockup</x:v>
@@ -1531,7 +1646,7 @@
         <x:v>Transactional indexation, policy and help links, consent, field labels, validation, recovery, order status, and customer support information.</x:v>
       </x:c>
       <x:c r="J10" s="20" t="str">
-        <x:v>Exact Purchase Path v1.6 was approved by Todd on August 31, 2026 and is ready for Rebekah's separate client review. Approval covers the cart, approved missing-photo cart treatment, empty-cart recovery, guest-checkout fields, validation, order review, customer-facing confirmation, and representative interactions. Live payment fields and failures, shipping rates, tax calculations, wallet options, fraud rules, transactional emails, inventory and order synchronization, final totals, and provider messages remain separate connected-service and Revel/Kosmos validation gates.</x:v>
+        <x:v>Exact Purchase Path v1.6 was approved by Todd and approved by Rebekah on September 2, 2026. Payment, shipping, tax, email, inventory, order, and provider behavior remain connected-service validation gates.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="96" hidden="0" customHeight="1">
@@ -1547,8 +1662,8 @@
       <x:c r="D11" s="20" t="str">
         <x:v>/my-account/ and child screens</x:v>
       </x:c>
-      <x:c r="E11" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E11" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F11" s="20" t="str">
         <x:v>Local page-body mockup</x:v>
@@ -1563,7 +1678,7 @@
         <x:v>Noindex account screens; privacy and consent; standard sign-in and password recovery, clear field labels, order access, address editing, and customer-safe support guidance.</x:v>
       </x:c>
       <x:c r="J11" s="20" t="str">
-        <x:v>Exact Customer Account System v1.6 was approved by Todd on September 1, 2026 and is ready for Rebekah's separate client review. Approval covers guest checkout, automatic optional account creation, standard email/password sign-in and recovery, dashboard, addresses, order history, order detail, representative interactions, and no customer 2FA. Staff/administrator backend security remains a separate staging task, and real email delivery, privacy/consent wording, order synchronization, and retention behavior remain implementation-validation gates.</x:v>
+        <x:v>Exact Customer Account System v1.6 was approved by Todd and approved by Rebekah on September 2, 2026. Staff/admin backend security and all connected-service behavior remain separate staging and implementation-validation gates.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="80" customHeight="1">
@@ -1579,8 +1694,8 @@
       <x:c r="D12" s="20" t="str">
         <x:v>Shared across store</x:v>
       </x:c>
-      <x:c r="E12" s="20" t="str">
-        <x:v>Internally Approved</x:v>
+      <x:c r="E12" s="131" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F12" s="20" t="str">
         <x:v>Local page-body mockup</x:v>
@@ -1595,7 +1710,7 @@
         <x:v>Honest stock/error language, accessible recovery actions, complete responsive behavior, keyboard/focus, labels, contrast, and reduced motion.</x:v>
       </x:c>
       <x:c r="J12" s="20" t="str">
-        <x:v>Exact Store States + Components v1.5 was approved by Todd on September 1, 2026 and is ready for Rebekah's separate client review. Approval covers all ten states, recovery actions, the approved sitewide missing-product-photo rule, loading treatment, mobile filter drawer, and responsive/accessibility checklist. Exact inventory, shipping, tax, payment-provider, authentication, and integration-error messages remain connected-service implementation-validation gates.</x:v>
+        <x:v>Exact Store States + Components v1.5 was approved by Todd and approved by Rebekah on September 2, 2026. Provider-specific messages remain connected-service implementation-validation inputs.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1623,7 +1738,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8533d231fb98460a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe9c3d02eca140ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1682,17 +1797,15 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E3" s="98" t="str">
-        <x:v>Pending client</x:v>
+        <x:v>Pending design</x:v>
       </x:c>
       <x:c r="F3" s="98" t="n">
-        <x:f>COUNTIF(C6:C16,"Pending client")</x:f>
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="98" t="str">
         <x:v>Gated later</x:v>
       </x:c>
       <x:c r="H3" s="98" t="n">
-        <x:f>COUNTIF(C6:C16,"External gate")+COUNTIF(C6:C16,"Future gated")</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1729,23 +1842,23 @@
       <x:c r="B6" s="114" t="str">
         <x:v>Exact mockup approval set</x:v>
       </x:c>
-      <x:c r="C6" s="114" t="str">
-        <x:v>Pending client</x:v>
+      <x:c r="C6" s="145" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D6" s="114" t="str">
-        <x:v>All seven systems are internally approved and frozen.</x:v>
+        <x:v>All seven exact systems are internally and client approved. Shop/Catalog v1.9 was confirmed September 3, 2026.</x:v>
       </x:c>
       <x:c r="E6" s="114" t="str">
-        <x:v>Review hub and version register show the exact current versions.</x:v>
+        <x:v>Exact-version email reply verified. No further design changes requested.</x:v>
       </x:c>
       <x:c r="F6" s="114" t="str">
-        <x:v>Rebekah approves all seven exact versions or requests a numbered revision.</x:v>
+        <x:v>Design gate complete. Obtain infrastructure authorization and confirm a safe working window.</x:v>
       </x:c>
       <x:c r="G6" s="114" t="str">
-        <x:v>Todd / Rebekah</x:v>
+        <x:v>Rebekah</x:v>
       </x:c>
       <x:c r="H6" s="114" t="str">
-        <x:v>phase-two-ecommerce-mockup-sheet.html</x:v>
+        <x:v>https://mail.google.com/mail/#all/1a069170a83b3a6e</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="66" customHeight="1">
@@ -1886,16 +1999,16 @@
         <x:v>Access and working-window verification</x:v>
       </x:c>
       <x:c r="C12" s="117" t="str">
-        <x:v>External gate</x:v>
+        <x:v>Access verified; working window pending</x:v>
       </x:c>
       <x:c r="D12" s="117" t="str">
-        <x:v>No external login during local preparation.</x:v>
+        <x:v>Blue Nova Revel access and the client-owned Kosmos dashboard login are verified. No connection or data pull has started.</x:v>
       </x:c>
       <x:c r="E12" s="117" t="str">
-        <x:v>Revel invite and client-owned Kosmos account are recorded; operational permissions and timing remain unverified.</x:v>
+        <x:v>Access records, support model, runbook, and one-product acceptance test are documented.</x:v>
       </x:c>
       <x:c r="F12" s="117" t="str">
-        <x:v>Verify Clarkston Revel permissions, Kosmos access/trial timing, one prepared product, and the working window.</x:v>
+        <x:v>Confirm the safe working window and representative test product before staging connection work.</x:v>
       </x:c>
       <x:c r="G12" s="117" t="str">
         <x:v>Todd / Rebekah / Blue Nova</x:v>
@@ -2350,7 +2463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e7a53d8dcc4383"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c86de70bd18420a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2947,7 +3060,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c02848e8ca34296"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1630584e632477d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3578,7 +3691,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7fa967d4f564ac7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac0ab156fffd47a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3602,7 +3715,7 @@
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>All seven exact current ecommerce mockup systems are internally approved and frozen while Rebekah reviews them. Local readiness documents and the dormant WooCommerce scaffold were completed September 2, 2026; external and staging work remains gated.</x:v>
+        <x:v>All seven exact systems are internally and client approved. Rebekah confirmed Shop/Catalog v1.9 on September 3, 2026. Local readiness documents and dormant scaffold are complete. Infrastructure authorization, working window, and connection testing remain separate gates.</x:v>
       </x:c>
       <x:c r="B2" s="28"/>
       <x:c r="C2" s="28"/>
@@ -3637,8 +3750,8 @@
       <x:c r="B5" s="20" t="str">
         <x:v>Approve global commerce add-on</x:v>
       </x:c>
-      <x:c r="C5" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C5" s="131" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
@@ -3647,7 +3760,7 @@
         <x:v>Exact Header + Footer Ecommerce Add-On v1.5 is internally approved and frozen. No WordPress implementation begins before Rebekah approves this version.</x:v>
       </x:c>
       <x:c r="F5" s="20" t="str">
-        <x:v>Rebekah approves exact system 01 v1.5</x:v>
+        <x:v>Exact version approved September 2, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="60" customHeight="1">
@@ -3657,8 +3770,8 @@
       <x:c r="B6" s="20" t="str">
         <x:v>Approve Online Store homepage</x:v>
       </x:c>
-      <x:c r="C6" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C6" s="131" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
@@ -3667,7 +3780,7 @@
         <x:v>Exact Main Homepage Ecommerce Integration v1.9 is internally approved and frozen. Its Shop Online control routes to the separate store page.</x:v>
       </x:c>
       <x:c r="F6" s="20" t="str">
-        <x:v>Rebekah approves exact system 02 v1.9</x:v>
+        <x:v>Exact version approved September 2, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="60" customHeight="1">
@@ -3677,17 +3790,17 @@
       <x:c r="B7" s="20" t="str">
         <x:v>Approve catalog template</x:v>
       </x:c>
-      <x:c r="C7" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C7" s="143" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
       </x:c>
       <x:c r="E7" s="20" t="str">
-        <x:v>Exact Shop Homepage + Product Catalog v1.8 is internally approved and frozen; connected product fields remain a later one-product validation task.</x:v>
+        <x:v>Exact Shop Homepage + Product Catalog v1.9 was approved by Todd on September 3, 2026 with Rebekah's two expandable filter groups; product mappings remain a later connected-data task.</x:v>
       </x:c>
       <x:c r="F7" s="20" t="str">
-        <x:v>Rebekah approves exact system 03 v1.8</x:v>
+        <x:v>Exact version approved September 3, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="60" customHeight="1">
@@ -3697,8 +3810,8 @@
       <x:c r="B8" s="20" t="str">
         <x:v>Approve product pages</x:v>
       </x:c>
-      <x:c r="C8" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C8" s="131" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
@@ -3707,7 +3820,7 @@
         <x:v>Exact Product Page Templates v1.7 is internally approved and frozen; connected data and verified source content remain later implementation gates.</x:v>
       </x:c>
       <x:c r="F8" s="20" t="str">
-        <x:v>Rebekah approves exact system 04 v1.7</x:v>
+        <x:v>Exact version approved September 2, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="60" customHeight="1">
@@ -3717,8 +3830,8 @@
       <x:c r="B9" s="20" t="str">
         <x:v>Approve purchase path</x:v>
       </x:c>
-      <x:c r="C9" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C9" s="131" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
@@ -3727,7 +3840,7 @@
         <x:v>Exact Purchase Path v1.6 is internally approved and frozen; payment, shipping, tax, email, and order behavior remain connected-service tests.</x:v>
       </x:c>
       <x:c r="F9" s="20" t="str">
-        <x:v>Rebekah approves exact system 05 v1.6</x:v>
+        <x:v>Exact version approved September 2, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="60" hidden="0" customHeight="1">
@@ -3737,8 +3850,8 @@
       <x:c r="B10" s="20" t="str">
         <x:v>Approve account system</x:v>
       </x:c>
-      <x:c r="C10" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C10" s="131" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
         <x:v>Blue Nova / Todd</x:v>
@@ -3747,7 +3860,7 @@
         <x:v>Exact Customer Account System v1.6 is internally approved and frozen with guest checkout, optional accounts, and no customer 2FA.</x:v>
       </x:c>
       <x:c r="F10" s="20" t="str">
-        <x:v>Rebekah approves exact system 06 v1.6</x:v>
+        <x:v>Exact version approved September 2, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="60" customHeight="1">
@@ -3757,8 +3870,8 @@
       <x:c r="B11" s="20" t="str">
         <x:v>Approve states + complete design QA</x:v>
       </x:c>
-      <x:c r="C11" s="20" t="str">
-        <x:v>Awaiting client approval</x:v>
+      <x:c r="C11" s="131" t="str">
+        <x:v>Client approved</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:v>Blue Nova / Todd / Rebekah</x:v>
@@ -3767,7 +3880,7 @@
         <x:v>Exact Store States + Components v1.5 is internally approved and frozen; provider-specific error text remains implementation validation.</x:v>
       </x:c>
       <x:c r="F11" s="20" t="str">
-        <x:v>Rebekah approves exact system 07 v1.5</x:v>
+        <x:v>Exact version approved September 2, 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="72" customHeight="1">
@@ -3897,7 +4010,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02bc2a6d1c34423d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc90ee954b7b4189"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4585,7 +4698,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd96fbfb9b2f420a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0270ef23a39a4090"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5041,7 +5154,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f189943e9a4e35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffd912edb5544f47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5106,17 +5219,16 @@
         <x:v>Awaiting client</x:v>
       </x:c>
       <x:c r="F3" s="44" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G3" s="41" t="str">
         <x:v>Client approved</x:v>
       </x:c>
       <x:c r="H3" s="44" t="n">
-        <x:f>COUNTIF(E6:E12,"Client Approved")</x:f>
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I3" s="45" t="str">
-        <x:v>Gates: Client approval</x:v>
+        <x:v>Design approved; infrastructure authorization next</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="28" customHeight="1">
@@ -5161,20 +5273,20 @@
       <x:c r="D6" s="55" t="str">
         <x:v>online-store-header-footer-add-on-v1.5.html</x:v>
       </x:c>
-      <x:c r="E6" s="55" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+      <x:c r="E6" s="134" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F6" s="55" t="str">
         <x:v>Approved by Todd</x:v>
       </x:c>
-      <x:c r="G6" s="55" t="str">
-        <x:v>Pending Rebekah</x:v>
+      <x:c r="G6" s="134" t="str">
+        <x:v>Approved by Rebekah 2026-09-02</x:v>
       </x:c>
       <x:c r="H6" s="57" t="str">
         <x:v>v1.6</x:v>
       </x:c>
       <x:c r="I6" s="55" t="str">
-        <x:v>Exact v1.5 internally approved September 2, 2026. The local header, tablet, and footer Online Store links open Shop Homepage + Product Catalog v1.8; production will use /shop/. v1.4 remains preserved as superseded history. Any later design change requires v1.6 and a new approval.</x:v>
+        <x:v>Exact v1.5 approved by Todd and Rebekah on September 2, 2026. Production Online Store links will use /shop/. Any later design change requires v1.6 and new exact-version approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="58" customHeight="1">
@@ -5190,23 +5302,23 @@
       <x:c r="D7" s="56" t="str">
         <x:v>main-homepage-ecommerce-integration-v1.9.html</x:v>
       </x:c>
-      <x:c r="E7" s="56" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+      <x:c r="E7" s="134" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F7" s="56" t="str">
         <x:v>Approved by Todd</x:v>
       </x:c>
-      <x:c r="G7" s="56" t="str">
-        <x:v>Pending Rebekah</x:v>
+      <x:c r="G7" s="134" t="str">
+        <x:v>Approved by Rebekah 2026-09-02</x:v>
       </x:c>
       <x:c r="H7" s="58" t="str">
         <x:v>v1.10</x:v>
       </x:c>
       <x:c r="I7" s="56" t="str">
-        <x:v>Exact v1.9 internally approved September 2, 2026. The Shop Online hero entry opens the separate Shop Homepage + Product Catalog v1.8 preview; production will use /shop/. It preserves the v1.8 numbering removal, approved imagery, copy, components, all other interactions, review-only addition labels, and page-body-only architecture. v1.8 is superseded without approval. Any later design change requires v1.10 and a new approval.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+        <x:v>Exact v1.9 approved by Todd and Rebekah on September 2, 2026. The Shop Online control routes directly to the separate Shop page. Any later design change requires v1.10 and new approval.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="115" customHeight="1">
       <x:c r="A8" s="57" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -5214,25 +5326,25 @@
         <x:v>Shop Homepage + Product Catalog</x:v>
       </x:c>
       <x:c r="C8" s="57" t="str">
-        <x:v>v1.8</x:v>
+        <x:v>v1.9</x:v>
       </x:c>
       <x:c r="D8" s="55" t="str">
-        <x:v>shop-catalog-template-v1.8.html</x:v>
-      </x:c>
-      <x:c r="E8" s="55" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+        <x:v>shop-catalog-template-v1.9.html</x:v>
+      </x:c>
+      <x:c r="E8" s="144" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F8" s="55" t="str">
-        <x:v>Approved by Todd</x:v>
-      </x:c>
-      <x:c r="G8" s="55" t="str">
-        <x:v>Pending Rebekah</x:v>
+        <x:v>Approved by Todd 2026-09-03</x:v>
+      </x:c>
+      <x:c r="G8" s="144" t="str">
+        <x:v>Approved by Rebekah 2026-09-03</x:v>
       </x:c>
       <x:c r="H8" s="57" t="str">
-        <x:v>v1.9</x:v>
+        <x:v>v1.10</x:v>
       </x:c>
       <x:c r="I8" s="55" t="str">
-        <x:v>Exact v1.8 internally approved August 31, 2026. Approval covers the complete catalog design and interactions shown in the mockup. Revel/Kosmos product data, sync, inventory, pricing, category mapping, real photography, and final content remain separate implementation-validation gates. Any later design change requires v1.9 and a new approval.</x:v>
+        <x:v>Exact v1.9 approved by Todd and Rebekah on September 3, 2026. Two expandable groups preserve the supplied nine brands and 21 wellness categories. Actual pilot choices and mappings remain connected-data validation. v1.8 remains superseded history. Source: https://mail.google.com/mail/#all/1a069170a83b3a6e</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -5248,20 +5360,20 @@
       <x:c r="D9" s="56" t="str">
         <x:v>product-page-templates-v1.7.html</x:v>
       </x:c>
-      <x:c r="E9" s="56" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+      <x:c r="E9" s="134" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F9" s="56" t="str">
         <x:v>Approved by Todd</x:v>
       </x:c>
-      <x:c r="G9" s="56" t="str">
-        <x:v>Pending Rebekah</x:v>
+      <x:c r="G9" s="134" t="str">
+        <x:v>Approved by Rebekah 2026-09-02</x:v>
       </x:c>
       <x:c r="H9" s="58" t="str">
         <x:v>v1.8</x:v>
       </x:c>
       <x:c r="I9" s="56" t="str">
-        <x:v>Exact v1.7 internally approved August 31, 2026. Approval covers the complete product-page design and interactions shown in the mockup. Revel/Kosmos product data, real photography, and verified manufacturer, supplier, label, or approved-catalog Directions &amp; Warnings remain separate implementation-validation gates. Any later design change requires v1.8 and a new approval.</x:v>
+        <x:v>Exact v1.7 approved by Todd and Rebekah. Connected product data, photography, and verified source content remain implementation-validation gates. Any later design change requires v1.8 and new approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="58" customHeight="1">
@@ -5277,20 +5389,20 @@
       <x:c r="D10" s="55" t="str">
         <x:v>purchase-path-mockup-v1.6.html</x:v>
       </x:c>
-      <x:c r="E10" s="55" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+      <x:c r="E10" s="134" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F10" s="55" t="str">
         <x:v>Approved by Todd</x:v>
       </x:c>
-      <x:c r="G10" s="55" t="str">
-        <x:v>Pending Rebekah</x:v>
+      <x:c r="G10" s="134" t="str">
+        <x:v>Approved by Rebekah 2026-09-02</x:v>
       </x:c>
       <x:c r="H10" s="57" t="str">
         <x:v>v1.7</x:v>
       </x:c>
       <x:c r="I10" s="55" t="str">
-        <x:v>Exact v1.6 internally approved August 31, 2026. Approval covers the complete cart-to-confirmation design and interactions shown in the mockup. Payment, shipping, tax, email, inventory, order, provider-message, and Revel/Kosmos behavior remain separate connected-service implementation-validation gates. Any later design change requires v1.7 and a new approval.</x:v>
+        <x:v>Exact v1.6 approved by Todd and Rebekah. Connected payment, shipping, tax, email, inventory, order, and provider behavior remain implementation-validation gates. Any later design change requires v1.7 and new approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="92.4000015258789" hidden="0" customHeight="1">
@@ -5306,20 +5418,20 @@
       <x:c r="D11" s="89" t="str">
         <x:v>customer-account-system-v1.6.html</x:v>
       </x:c>
-      <x:c r="E11" s="89" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+      <x:c r="E11" s="134" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F11" s="89" t="str">
         <x:v>Approved by Todd</x:v>
       </x:c>
-      <x:c r="G11" s="89" t="str">
-        <x:v>Pending Rebekah</x:v>
+      <x:c r="G11" s="134" t="str">
+        <x:v>Approved by Rebekah 2026-09-02</x:v>
       </x:c>
       <x:c r="H11" s="88" t="str">
         <x:v>v1.7</x:v>
       </x:c>
       <x:c r="I11" s="89" t="str">
-        <x:v>Exact v1.6 internally approved September 1, 2026. Approval covers guest checkout, automatic optional customer accounts, standard sign-in and recovery, dashboard, addresses, orders, order detail, representative interactions, and no customer 2FA. Staff/administrator backend security and all connected-service behavior remain separate staging and implementation-validation gates. Any later design change requires v1.7 and a new approval.</x:v>
+        <x:v>Exact v1.6 approved by Todd and Rebekah. Staff/admin security and connected-service behavior remain later staging validation. Any later design change requires v1.7 and new approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="58" customHeight="1">
@@ -5335,20 +5447,20 @@
       <x:c r="D12" s="55" t="str">
         <x:v>store-states-components-v1.5.html</x:v>
       </x:c>
-      <x:c r="E12" s="55" t="str">
-        <x:v>Awaiting Client Approval</x:v>
+      <x:c r="E12" s="134" t="str">
+        <x:v>Client Approved</x:v>
       </x:c>
       <x:c r="F12" s="55" t="str">
         <x:v>Approved by Todd</x:v>
       </x:c>
-      <x:c r="G12" s="55" t="str">
-        <x:v>Pending Rebekah</x:v>
+      <x:c r="G12" s="134" t="str">
+        <x:v>Approved by Rebekah 2026-09-02</x:v>
       </x:c>
       <x:c r="H12" s="57" t="str">
         <x:v>v1.6</x:v>
       </x:c>
       <x:c r="I12" s="55" t="str">
-        <x:v>Exact v1.5 internally approved September 1, 2026. Approval covers no-results, empty-filter, out-of-stock, unavailable-variation, approved missing-photo, loading, empty-cart, checkout-validation, payment-failure, mobile-filter, and responsive/accessibility states. Connected-service wording remains an implementation-validation gate. Any later design change requires v1.6 and a new approval.</x:v>
+        <x:v>Exact v1.5 approved by Todd and Rebekah. Provider-specific messages remain later validation inputs. Any later design change requires v1.6 and new approval.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
@@ -5881,7 +5993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0643dc1ae5b843bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8a5657b4fa24010"/>
   </x:tableParts>
 </x:worksheet>
 </file>